--- a/exports/golf_prices_20260420.xlsx
+++ b/exports/golf_prices_20260420.xlsx
@@ -506,7 +506,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-20 08:38:35</t>
+          <t>2026-04-20 20:59:40</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -553,10 +553,10 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>146664</v>
+        <v>145965</v>
       </c>
       <c r="L2" t="n">
-        <v>99.64</v>
+        <v>99.25</v>
       </c>
       <c r="M2" t="b">
         <v>1</v>
@@ -577,7 +577,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-20 08:38:35</t>
+          <t>2026-04-20 20:59:40</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -624,10 +624,10 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>146664</v>
+        <v>145965</v>
       </c>
       <c r="L3" t="n">
-        <v>99.64</v>
+        <v>99.25</v>
       </c>
       <c r="M3" t="b">
         <v>1</v>
@@ -648,7 +648,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-20 08:38:37</t>
+          <t>2026-04-20 20:59:42</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -695,10 +695,10 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>146664</v>
+        <v>145965</v>
       </c>
       <c r="L4" t="n">
-        <v>99.64</v>
+        <v>99.25</v>
       </c>
       <c r="M4" t="b">
         <v>1</v>
@@ -719,7 +719,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-20 08:38:37</t>
+          <t>2026-04-20 20:59:42</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -766,10 +766,10 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>146664</v>
+        <v>145965</v>
       </c>
       <c r="L5" t="n">
-        <v>99.64</v>
+        <v>99.25</v>
       </c>
       <c r="M5" t="b">
         <v>1</v>
@@ -790,7 +790,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-20 08:38:39</t>
+          <t>2026-04-20 20:59:44</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -837,10 +837,10 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>146664</v>
+        <v>145965</v>
       </c>
       <c r="L6" t="n">
-        <v>99.64</v>
+        <v>99.25</v>
       </c>
       <c r="M6" t="b">
         <v>1</v>
@@ -861,7 +861,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-20 08:38:39</t>
+          <t>2026-04-20 20:59:44</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -908,10 +908,10 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>146664</v>
+        <v>145965</v>
       </c>
       <c r="L7" t="n">
-        <v>99.64</v>
+        <v>99.25</v>
       </c>
       <c r="M7" t="b">
         <v>1</v>
@@ -932,7 +932,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-20 08:38:41</t>
+          <t>2026-04-20 20:59:46</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>146664</v>
+        <v>145965</v>
       </c>
       <c r="L8" t="n">
-        <v>99.64</v>
+        <v>99.25</v>
       </c>
       <c r="M8" t="b">
         <v>1</v>
@@ -1003,7 +1003,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-20 08:38:41</t>
+          <t>2026-04-20 20:59:46</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1050,10 +1050,10 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>146664</v>
+        <v>145965</v>
       </c>
       <c r="L9" t="n">
-        <v>99.64</v>
+        <v>99.25</v>
       </c>
       <c r="M9" t="b">
         <v>1</v>
@@ -1074,7 +1074,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-20 08:38:43</t>
+          <t>2026-04-20 20:59:47</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1121,10 +1121,10 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>177219</v>
+        <v>176375</v>
       </c>
       <c r="L10" t="n">
-        <v>120.4</v>
+        <v>119.93</v>
       </c>
       <c r="M10" t="b">
         <v>1</v>
@@ -1145,7 +1145,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-20 08:38:43</t>
+          <t>2026-04-20 20:59:47</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>177219</v>
+        <v>176375</v>
       </c>
       <c r="L11" t="n">
-        <v>120.4</v>
+        <v>119.93</v>
       </c>
       <c r="M11" t="b">
         <v>1</v>
@@ -1216,7 +1216,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-20 08:38:44</t>
+          <t>2026-04-20 20:59:49</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1263,10 +1263,10 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>177219</v>
+        <v>176375</v>
       </c>
       <c r="L12" t="n">
-        <v>120.4</v>
+        <v>119.93</v>
       </c>
       <c r="M12" t="b">
         <v>1</v>
@@ -1287,7 +1287,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-20 08:38:44</t>
+          <t>2026-04-20 20:59:49</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1334,10 +1334,10 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>177219</v>
+        <v>176375</v>
       </c>
       <c r="L13" t="n">
-        <v>120.4</v>
+        <v>119.93</v>
       </c>
       <c r="M13" t="b">
         <v>1</v>
@@ -1358,7 +1358,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-20 08:38:46</t>
+          <t>2026-04-20 20:59:51</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1405,10 +1405,10 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>177219</v>
+        <v>176375</v>
       </c>
       <c r="L14" t="n">
-        <v>120.4</v>
+        <v>119.93</v>
       </c>
       <c r="M14" t="b">
         <v>1</v>
@@ -1429,7 +1429,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-20 08:38:46</t>
+          <t>2026-04-20 20:59:51</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1476,10 +1476,10 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>177219</v>
+        <v>176375</v>
       </c>
       <c r="L15" t="n">
-        <v>120.4</v>
+        <v>119.93</v>
       </c>
       <c r="M15" t="b">
         <v>1</v>
@@ -1500,7 +1500,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-20 08:38:48</t>
+          <t>2026-04-20 20:59:53</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1547,10 +1547,10 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>146664</v>
+        <v>145965</v>
       </c>
       <c r="L16" t="n">
-        <v>99.64</v>
+        <v>99.25</v>
       </c>
       <c r="M16" t="b">
         <v>1</v>
@@ -1571,7 +1571,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-20 08:38:48</t>
+          <t>2026-04-20 20:59:53</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1618,10 +1618,10 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>146664</v>
+        <v>145965</v>
       </c>
       <c r="L17" t="n">
-        <v>99.64</v>
+        <v>99.25</v>
       </c>
       <c r="M17" t="b">
         <v>1</v>
@@ -1642,7 +1642,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-20 08:38:50</t>
+          <t>2026-04-20 20:59:55</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1689,10 +1689,10 @@
         </is>
       </c>
       <c r="K18" t="n">
-        <v>146664</v>
+        <v>145965</v>
       </c>
       <c r="L18" t="n">
-        <v>99.64</v>
+        <v>99.25</v>
       </c>
       <c r="M18" t="b">
         <v>1</v>
@@ -1713,7 +1713,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-20 08:38:50</t>
+          <t>2026-04-20 20:59:55</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1760,10 +1760,10 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>146664</v>
+        <v>145965</v>
       </c>
       <c r="L19" t="n">
-        <v>99.64</v>
+        <v>99.25</v>
       </c>
       <c r="M19" t="b">
         <v>1</v>
@@ -1784,7 +1784,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-20 08:38:52</t>
+          <t>2026-04-20 20:59:57</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1831,10 +1831,10 @@
         </is>
       </c>
       <c r="K20" t="n">
-        <v>177219</v>
+        <v>176375</v>
       </c>
       <c r="L20" t="n">
-        <v>120.4</v>
+        <v>119.93</v>
       </c>
       <c r="M20" t="b">
         <v>1</v>
@@ -1855,7 +1855,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-20 08:38:52</t>
+          <t>2026-04-20 20:59:57</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1902,10 +1902,10 @@
         </is>
       </c>
       <c r="K21" t="n">
-        <v>177219</v>
+        <v>176375</v>
       </c>
       <c r="L21" t="n">
-        <v>120.4</v>
+        <v>119.93</v>
       </c>
       <c r="M21" t="b">
         <v>1</v>
@@ -1926,7 +1926,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-20 08:38:54</t>
+          <t>2026-04-20 20:59:59</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1973,10 +1973,10 @@
         </is>
       </c>
       <c r="K22" t="n">
-        <v>177219</v>
+        <v>176375</v>
       </c>
       <c r="L22" t="n">
-        <v>120.4</v>
+        <v>119.93</v>
       </c>
       <c r="M22" t="b">
         <v>1</v>
@@ -1997,7 +1997,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-04-20 08:38:54</t>
+          <t>2026-04-20 20:59:59</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2044,10 +2044,10 @@
         </is>
       </c>
       <c r="K23" t="n">
-        <v>177219</v>
+        <v>176375</v>
       </c>
       <c r="L23" t="n">
-        <v>120.4</v>
+        <v>119.93</v>
       </c>
       <c r="M23" t="b">
         <v>1</v>
@@ -2068,7 +2068,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-04-20 08:38:56</t>
+          <t>2026-04-20 21:00:01</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="K24" t="n">
-        <v>177219</v>
+        <v>176375</v>
       </c>
       <c r="L24" t="n">
-        <v>120.4</v>
+        <v>119.93</v>
       </c>
       <c r="M24" t="b">
         <v>1</v>
@@ -2139,7 +2139,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-04-20 08:38:56</t>
+          <t>2026-04-20 21:00:01</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2186,10 +2186,10 @@
         </is>
       </c>
       <c r="K25" t="n">
-        <v>177219</v>
+        <v>176375</v>
       </c>
       <c r="L25" t="n">
-        <v>120.4</v>
+        <v>119.93</v>
       </c>
       <c r="M25" t="b">
         <v>1</v>
@@ -2210,7 +2210,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-04-20 08:38:58</t>
+          <t>2026-04-20 21:00:03</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2257,10 +2257,10 @@
         </is>
       </c>
       <c r="K26" t="n">
-        <v>177219</v>
+        <v>176375</v>
       </c>
       <c r="L26" t="n">
-        <v>120.4</v>
+        <v>119.93</v>
       </c>
       <c r="M26" t="b">
         <v>1</v>
@@ -2281,7 +2281,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-04-20 08:38:58</t>
+          <t>2026-04-20 21:00:03</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2328,10 +2328,10 @@
         </is>
       </c>
       <c r="K27" t="n">
-        <v>177219</v>
+        <v>176375</v>
       </c>
       <c r="L27" t="n">
-        <v>120.4</v>
+        <v>119.93</v>
       </c>
       <c r="M27" t="b">
         <v>1</v>
@@ -2352,7 +2352,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-04-20 08:38:59</t>
+          <t>2026-04-20 21:00:05</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2399,10 +2399,10 @@
         </is>
       </c>
       <c r="K28" t="n">
-        <v>146664</v>
+        <v>145965</v>
       </c>
       <c r="L28" t="n">
-        <v>99.64</v>
+        <v>99.25</v>
       </c>
       <c r="M28" t="b">
         <v>1</v>
@@ -2423,7 +2423,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-04-20 08:38:59</t>
+          <t>2026-04-20 21:00:05</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2470,10 +2470,10 @@
         </is>
       </c>
       <c r="K29" t="n">
-        <v>146664</v>
+        <v>145965</v>
       </c>
       <c r="L29" t="n">
-        <v>99.64</v>
+        <v>99.25</v>
       </c>
       <c r="M29" t="b">
         <v>1</v>
@@ -2494,7 +2494,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-20 08:39:01</t>
+          <t>2026-04-20 21:00:07</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2541,10 +2541,10 @@
         </is>
       </c>
       <c r="K30" t="n">
-        <v>119164</v>
+        <v>118597</v>
       </c>
       <c r="L30" t="n">
-        <v>80.95999999999999</v>
+        <v>80.64</v>
       </c>
       <c r="M30" t="b">
         <v>1</v>
@@ -2565,7 +2565,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-20 08:39:01</t>
+          <t>2026-04-20 21:00:07</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2612,10 +2612,10 @@
         </is>
       </c>
       <c r="K31" t="n">
-        <v>119164</v>
+        <v>118597</v>
       </c>
       <c r="L31" t="n">
-        <v>80.95999999999999</v>
+        <v>80.64</v>
       </c>
       <c r="M31" t="b">
         <v>1</v>
@@ -2636,7 +2636,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-20 08:39:03</t>
+          <t>2026-04-20 21:00:09</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2683,10 +2683,10 @@
         </is>
       </c>
       <c r="K32" t="n">
-        <v>119164</v>
+        <v>118597</v>
       </c>
       <c r="L32" t="n">
-        <v>80.95999999999999</v>
+        <v>80.64</v>
       </c>
       <c r="M32" t="b">
         <v>1</v>
@@ -2707,7 +2707,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-20 08:39:03</t>
+          <t>2026-04-20 21:00:09</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2754,10 +2754,10 @@
         </is>
       </c>
       <c r="K33" t="n">
-        <v>119164</v>
+        <v>118597</v>
       </c>
       <c r="L33" t="n">
-        <v>80.95999999999999</v>
+        <v>80.64</v>
       </c>
       <c r="M33" t="b">
         <v>1</v>
@@ -2778,7 +2778,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-20 08:39:05</t>
+          <t>2026-04-20 21:00:11</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2825,10 +2825,10 @@
         </is>
       </c>
       <c r="K34" t="n">
-        <v>119164</v>
+        <v>118597</v>
       </c>
       <c r="L34" t="n">
-        <v>80.95999999999999</v>
+        <v>80.64</v>
       </c>
       <c r="M34" t="b">
         <v>1</v>
@@ -2849,7 +2849,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-20 08:39:05</t>
+          <t>2026-04-20 21:00:11</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2896,10 +2896,10 @@
         </is>
       </c>
       <c r="K35" t="n">
-        <v>119164</v>
+        <v>118597</v>
       </c>
       <c r="L35" t="n">
-        <v>80.95999999999999</v>
+        <v>80.64</v>
       </c>
       <c r="M35" t="b">
         <v>1</v>
@@ -2920,7 +2920,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-20 08:39:07</t>
+          <t>2026-04-20 21:00:13</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="K36" t="n">
-        <v>119164</v>
+        <v>118597</v>
       </c>
       <c r="L36" t="n">
-        <v>80.95999999999999</v>
+        <v>80.64</v>
       </c>
       <c r="M36" t="b">
         <v>1</v>
@@ -2991,7 +2991,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-20 08:39:07</t>
+          <t>2026-04-20 21:00:13</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3038,10 +3038,10 @@
         </is>
       </c>
       <c r="K37" t="n">
-        <v>119164</v>
+        <v>118597</v>
       </c>
       <c r="L37" t="n">
-        <v>80.95999999999999</v>
+        <v>80.64</v>
       </c>
       <c r="M37" t="b">
         <v>1</v>
@@ -3062,7 +3062,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-04-20 08:39:09</t>
+          <t>2026-04-20 21:00:15</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3109,10 +3109,10 @@
         </is>
       </c>
       <c r="K38" t="n">
-        <v>161941</v>
+        <v>161170</v>
       </c>
       <c r="L38" t="n">
-        <v>110.02</v>
+        <v>109.59</v>
       </c>
       <c r="M38" t="b">
         <v>1</v>
@@ -3133,7 +3133,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-04-20 08:39:09</t>
+          <t>2026-04-20 21:00:15</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="K39" t="n">
-        <v>161941</v>
+        <v>161170</v>
       </c>
       <c r="L39" t="n">
-        <v>110.02</v>
+        <v>109.59</v>
       </c>
       <c r="M39" t="b">
         <v>1</v>
@@ -3204,7 +3204,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-04-20 08:39:11</t>
+          <t>2026-04-20 21:00:17</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3251,10 +3251,10 @@
         </is>
       </c>
       <c r="K40" t="n">
-        <v>180274</v>
+        <v>179416</v>
       </c>
       <c r="L40" t="n">
-        <v>122.47</v>
+        <v>121.99</v>
       </c>
       <c r="M40" t="b">
         <v>1</v>
@@ -3275,7 +3275,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-04-20 08:39:11</t>
+          <t>2026-04-20 21:00:17</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3322,10 +3322,10 @@
         </is>
       </c>
       <c r="K41" t="n">
-        <v>180274</v>
+        <v>179416</v>
       </c>
       <c r="L41" t="n">
-        <v>122.47</v>
+        <v>121.99</v>
       </c>
       <c r="M41" t="b">
         <v>1</v>
@@ -3346,7 +3346,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-04-20 08:39:13</t>
+          <t>2026-04-20 21:00:19</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3393,10 +3393,10 @@
         </is>
       </c>
       <c r="K42" t="n">
-        <v>119164</v>
+        <v>118597</v>
       </c>
       <c r="L42" t="n">
-        <v>80.95999999999999</v>
+        <v>80.64</v>
       </c>
       <c r="M42" t="b">
         <v>1</v>
@@ -3417,7 +3417,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-04-20 08:39:13</t>
+          <t>2026-04-20 21:00:19</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3464,10 +3464,10 @@
         </is>
       </c>
       <c r="K43" t="n">
-        <v>119164</v>
+        <v>118597</v>
       </c>
       <c r="L43" t="n">
-        <v>80.95999999999999</v>
+        <v>80.64</v>
       </c>
       <c r="M43" t="b">
         <v>1</v>
@@ -3488,7 +3488,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-04-20 08:39:15</t>
+          <t>2026-04-20 21:00:21</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3535,10 +3535,10 @@
         </is>
       </c>
       <c r="K44" t="n">
-        <v>119164</v>
+        <v>118597</v>
       </c>
       <c r="L44" t="n">
-        <v>80.95999999999999</v>
+        <v>80.64</v>
       </c>
       <c r="M44" t="b">
         <v>1</v>
@@ -3559,7 +3559,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-04-20 08:39:15</t>
+          <t>2026-04-20 21:00:21</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3606,10 +3606,10 @@
         </is>
       </c>
       <c r="K45" t="n">
-        <v>119164</v>
+        <v>118597</v>
       </c>
       <c r="L45" t="n">
-        <v>80.95999999999999</v>
+        <v>80.64</v>
       </c>
       <c r="M45" t="b">
         <v>1</v>
@@ -3630,7 +3630,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-04-20 08:39:17</t>
+          <t>2026-04-20 21:00:23</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3677,10 +3677,10 @@
         </is>
       </c>
       <c r="K46" t="n">
-        <v>119164</v>
+        <v>118597</v>
       </c>
       <c r="L46" t="n">
-        <v>80.95999999999999</v>
+        <v>80.64</v>
       </c>
       <c r="M46" t="b">
         <v>1</v>
@@ -3701,7 +3701,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-04-20 08:39:17</t>
+          <t>2026-04-20 21:00:23</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3748,10 +3748,10 @@
         </is>
       </c>
       <c r="K47" t="n">
-        <v>119164</v>
+        <v>118597</v>
       </c>
       <c r="L47" t="n">
-        <v>80.95999999999999</v>
+        <v>80.64</v>
       </c>
       <c r="M47" t="b">
         <v>1</v>
@@ -3772,7 +3772,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-04-20 08:39:19</t>
+          <t>2026-04-20 21:00:25</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3819,10 +3819,10 @@
         </is>
       </c>
       <c r="K48" t="n">
-        <v>180274</v>
+        <v>179416</v>
       </c>
       <c r="L48" t="n">
-        <v>122.47</v>
+        <v>121.99</v>
       </c>
       <c r="M48" t="b">
         <v>1</v>
@@ -3843,7 +3843,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-04-20 08:39:19</t>
+          <t>2026-04-20 21:00:25</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3890,10 +3890,10 @@
         </is>
       </c>
       <c r="K49" t="n">
-        <v>180274</v>
+        <v>179416</v>
       </c>
       <c r="L49" t="n">
-        <v>122.47</v>
+        <v>121.99</v>
       </c>
       <c r="M49" t="b">
         <v>1</v>
@@ -3914,7 +3914,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-04-20 08:39:21</t>
+          <t>2026-04-20 21:00:27</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="K50" t="n">
-        <v>180274</v>
+        <v>179416</v>
       </c>
       <c r="L50" t="n">
-        <v>122.47</v>
+        <v>121.99</v>
       </c>
       <c r="M50" t="b">
         <v>1</v>
@@ -3985,7 +3985,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-04-20 08:39:21</t>
+          <t>2026-04-20 21:00:27</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4032,10 +4032,10 @@
         </is>
       </c>
       <c r="K51" t="n">
-        <v>180274</v>
+        <v>179416</v>
       </c>
       <c r="L51" t="n">
-        <v>122.47</v>
+        <v>121.99</v>
       </c>
       <c r="M51" t="b">
         <v>1</v>
@@ -4056,7 +4056,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-04-20 08:39:22</t>
+          <t>2026-04-20 21:00:28</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4103,10 +4103,10 @@
         </is>
       </c>
       <c r="K52" t="n">
-        <v>161941</v>
+        <v>161170</v>
       </c>
       <c r="L52" t="n">
-        <v>110.02</v>
+        <v>109.59</v>
       </c>
       <c r="M52" t="b">
         <v>1</v>
@@ -4127,7 +4127,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-04-20 08:39:22</t>
+          <t>2026-04-20 21:00:28</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4174,10 +4174,10 @@
         </is>
       </c>
       <c r="K53" t="n">
-        <v>161941</v>
+        <v>161170</v>
       </c>
       <c r="L53" t="n">
-        <v>110.02</v>
+        <v>109.59</v>
       </c>
       <c r="M53" t="b">
         <v>1</v>
@@ -4198,7 +4198,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-04-20 08:39:25</t>
+          <t>2026-04-20 21:00:30</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4245,10 +4245,10 @@
         </is>
       </c>
       <c r="K54" t="n">
-        <v>161941</v>
+        <v>161170</v>
       </c>
       <c r="L54" t="n">
-        <v>110.02</v>
+        <v>109.59</v>
       </c>
       <c r="M54" t="b">
         <v>1</v>
@@ -4269,7 +4269,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-04-20 08:39:25</t>
+          <t>2026-04-20 21:00:30</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4316,10 +4316,10 @@
         </is>
       </c>
       <c r="K55" t="n">
-        <v>161941</v>
+        <v>161170</v>
       </c>
       <c r="L55" t="n">
-        <v>110.02</v>
+        <v>109.59</v>
       </c>
       <c r="M55" t="b">
         <v>1</v>
@@ -4340,7 +4340,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-04-20 08:39:26</t>
+          <t>2026-04-20 21:00:32</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4387,10 +4387,10 @@
         </is>
       </c>
       <c r="K56" t="n">
-        <v>119164</v>
+        <v>118597</v>
       </c>
       <c r="L56" t="n">
-        <v>80.95999999999999</v>
+        <v>80.64</v>
       </c>
       <c r="M56" t="b">
         <v>1</v>
@@ -4411,7 +4411,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-04-20 08:39:26</t>
+          <t>2026-04-20 21:00:32</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4458,10 +4458,10 @@
         </is>
       </c>
       <c r="K57" t="n">
-        <v>119164</v>
+        <v>118597</v>
       </c>
       <c r="L57" t="n">
-        <v>80.95999999999999</v>
+        <v>80.64</v>
       </c>
       <c r="M57" t="b">
         <v>1</v>
@@ -4482,7 +4482,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-04-20 08:39:28</t>
+          <t>2026-04-20 21:00:34</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4529,10 +4529,10 @@
         </is>
       </c>
       <c r="K58" t="n">
-        <v>131386</v>
+        <v>130552</v>
       </c>
       <c r="L58" t="n">
-        <v>89.26000000000001</v>
+        <v>88.77</v>
       </c>
       <c r="M58" t="b">
         <v>1</v>
@@ -4553,7 +4553,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-04-20 08:39:28</t>
+          <t>2026-04-20 21:00:34</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4600,10 +4600,10 @@
         </is>
       </c>
       <c r="K59" t="n">
-        <v>131386</v>
+        <v>130552</v>
       </c>
       <c r="L59" t="n">
-        <v>89.26000000000001</v>
+        <v>88.77</v>
       </c>
       <c r="M59" t="b">
         <v>1</v>
@@ -4624,7 +4624,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-04-20 08:39:30</t>
+          <t>2026-04-20 21:00:36</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4671,10 +4671,10 @@
         </is>
       </c>
       <c r="K60" t="n">
-        <v>131386</v>
+        <v>130552</v>
       </c>
       <c r="L60" t="n">
-        <v>89.26000000000001</v>
+        <v>88.77</v>
       </c>
       <c r="M60" t="b">
         <v>1</v>
@@ -4695,7 +4695,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-04-20 08:39:30</t>
+          <t>2026-04-20 21:00:36</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4742,10 +4742,10 @@
         </is>
       </c>
       <c r="K61" t="n">
-        <v>131386</v>
+        <v>130552</v>
       </c>
       <c r="L61" t="n">
-        <v>89.26000000000001</v>
+        <v>88.77</v>
       </c>
       <c r="M61" t="b">
         <v>1</v>
@@ -4766,7 +4766,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-04-20 08:39:32</t>
+          <t>2026-04-20 21:00:38</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4813,10 +4813,10 @@
         </is>
       </c>
       <c r="K62" t="n">
-        <v>131386</v>
+        <v>130552</v>
       </c>
       <c r="L62" t="n">
-        <v>89.26000000000001</v>
+        <v>88.77</v>
       </c>
       <c r="M62" t="b">
         <v>1</v>
@@ -4837,7 +4837,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-04-20 08:39:32</t>
+          <t>2026-04-20 21:00:38</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4884,10 +4884,10 @@
         </is>
       </c>
       <c r="K63" t="n">
-        <v>131386</v>
+        <v>130552</v>
       </c>
       <c r="L63" t="n">
-        <v>89.26000000000001</v>
+        <v>88.77</v>
       </c>
       <c r="M63" t="b">
         <v>1</v>
@@ -4908,7 +4908,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-04-20 08:39:34</t>
+          <t>2026-04-20 21:00:40</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4955,10 +4955,10 @@
         </is>
       </c>
       <c r="K64" t="n">
-        <v>131386</v>
+        <v>130552</v>
       </c>
       <c r="L64" t="n">
-        <v>89.26000000000001</v>
+        <v>88.77</v>
       </c>
       <c r="M64" t="b">
         <v>1</v>
@@ -4979,7 +4979,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-04-20 08:39:34</t>
+          <t>2026-04-20 21:00:40</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5026,10 +5026,10 @@
         </is>
       </c>
       <c r="K65" t="n">
-        <v>131386</v>
+        <v>130552</v>
       </c>
       <c r="L65" t="n">
-        <v>89.26000000000001</v>
+        <v>88.77</v>
       </c>
       <c r="M65" t="b">
         <v>1</v>
@@ -5050,7 +5050,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-04-20 08:39:36</t>
+          <t>2026-04-20 21:00:42</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5097,10 +5097,10 @@
         </is>
       </c>
       <c r="K66" t="n">
-        <v>168052</v>
+        <v>166985</v>
       </c>
       <c r="L66" t="n">
-        <v>114.17</v>
+        <v>113.54</v>
       </c>
       <c r="M66" t="b">
         <v>1</v>
@@ -5121,7 +5121,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-04-20 08:39:36</t>
+          <t>2026-04-20 21:00:42</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5168,10 +5168,10 @@
         </is>
       </c>
       <c r="K67" t="n">
-        <v>168052</v>
+        <v>166985</v>
       </c>
       <c r="L67" t="n">
-        <v>114.17</v>
+        <v>113.54</v>
       </c>
       <c r="M67" t="b">
         <v>1</v>
@@ -5192,7 +5192,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-04-20 08:39:38</t>
+          <t>2026-04-20 21:00:44</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5239,10 +5239,10 @@
         </is>
       </c>
       <c r="K68" t="n">
-        <v>168052</v>
+        <v>166985</v>
       </c>
       <c r="L68" t="n">
-        <v>114.17</v>
+        <v>113.54</v>
       </c>
       <c r="M68" t="b">
         <v>1</v>
@@ -5263,7 +5263,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-04-20 08:39:38</t>
+          <t>2026-04-20 21:00:44</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5310,10 +5310,10 @@
         </is>
       </c>
       <c r="K69" t="n">
-        <v>168052</v>
+        <v>166985</v>
       </c>
       <c r="L69" t="n">
-        <v>114.17</v>
+        <v>113.54</v>
       </c>
       <c r="M69" t="b">
         <v>1</v>
@@ -5334,7 +5334,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-04-20 08:39:40</t>
+          <t>2026-04-20 21:00:46</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5381,10 +5381,10 @@
         </is>
       </c>
       <c r="K70" t="n">
-        <v>168052</v>
+        <v>166985</v>
       </c>
       <c r="L70" t="n">
-        <v>114.17</v>
+        <v>113.54</v>
       </c>
       <c r="M70" t="b">
         <v>1</v>
@@ -5405,7 +5405,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-04-20 08:39:40</t>
+          <t>2026-04-20 21:00:46</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5452,10 +5452,10 @@
         </is>
       </c>
       <c r="K71" t="n">
-        <v>168052</v>
+        <v>166985</v>
       </c>
       <c r="L71" t="n">
-        <v>114.17</v>
+        <v>113.54</v>
       </c>
       <c r="M71" t="b">
         <v>1</v>
@@ -5476,7 +5476,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-04-20 08:39:41</t>
+          <t>2026-04-20 21:00:48</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5523,10 +5523,10 @@
         </is>
       </c>
       <c r="K72" t="n">
-        <v>131386</v>
+        <v>130552</v>
       </c>
       <c r="L72" t="n">
-        <v>89.26000000000001</v>
+        <v>88.77</v>
       </c>
       <c r="M72" t="b">
         <v>1</v>
@@ -5547,7 +5547,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-04-20 08:39:41</t>
+          <t>2026-04-20 21:00:48</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5594,10 +5594,10 @@
         </is>
       </c>
       <c r="K73" t="n">
-        <v>131386</v>
+        <v>130552</v>
       </c>
       <c r="L73" t="n">
-        <v>89.26000000000001</v>
+        <v>88.77</v>
       </c>
       <c r="M73" t="b">
         <v>1</v>
@@ -5618,7 +5618,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-04-20 08:39:43</t>
+          <t>2026-04-20 21:00:50</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5665,10 +5665,10 @@
         </is>
       </c>
       <c r="K74" t="n">
-        <v>131386</v>
+        <v>130552</v>
       </c>
       <c r="L74" t="n">
-        <v>89.26000000000001</v>
+        <v>88.77</v>
       </c>
       <c r="M74" t="b">
         <v>1</v>
@@ -5689,7 +5689,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-04-20 08:39:43</t>
+          <t>2026-04-20 21:00:50</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5736,10 +5736,10 @@
         </is>
       </c>
       <c r="K75" t="n">
-        <v>131386</v>
+        <v>130552</v>
       </c>
       <c r="L75" t="n">
-        <v>89.26000000000001</v>
+        <v>88.77</v>
       </c>
       <c r="M75" t="b">
         <v>1</v>
@@ -5760,7 +5760,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-04-20 08:39:45</t>
+          <t>2026-04-20 21:00:51</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5807,10 +5807,10 @@
         </is>
       </c>
       <c r="K76" t="n">
-        <v>168052</v>
+        <v>166985</v>
       </c>
       <c r="L76" t="n">
-        <v>114.17</v>
+        <v>113.54</v>
       </c>
       <c r="M76" t="b">
         <v>1</v>
@@ -5831,7 +5831,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-04-20 08:39:45</t>
+          <t>2026-04-20 21:00:51</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5878,10 +5878,10 @@
         </is>
       </c>
       <c r="K77" t="n">
-        <v>168052</v>
+        <v>166985</v>
       </c>
       <c r="L77" t="n">
-        <v>114.17</v>
+        <v>113.54</v>
       </c>
       <c r="M77" t="b">
         <v>1</v>
@@ -5902,7 +5902,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-04-20 08:39:47</t>
+          <t>2026-04-20 21:00:53</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5949,10 +5949,10 @@
         </is>
       </c>
       <c r="K78" t="n">
-        <v>168052</v>
+        <v>166985</v>
       </c>
       <c r="L78" t="n">
-        <v>114.17</v>
+        <v>113.54</v>
       </c>
       <c r="M78" t="b">
         <v>1</v>
@@ -5973,7 +5973,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-04-20 08:39:47</t>
+          <t>2026-04-20 21:00:53</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6020,10 +6020,10 @@
         </is>
       </c>
       <c r="K79" t="n">
-        <v>168052</v>
+        <v>166985</v>
       </c>
       <c r="L79" t="n">
-        <v>114.17</v>
+        <v>113.54</v>
       </c>
       <c r="M79" t="b">
         <v>1</v>
@@ -6044,7 +6044,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-04-20 08:39:49</t>
+          <t>2026-04-20 21:00:55</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6091,10 +6091,10 @@
         </is>
       </c>
       <c r="K80" t="n">
-        <v>168052</v>
+        <v>166985</v>
       </c>
       <c r="L80" t="n">
-        <v>114.17</v>
+        <v>113.54</v>
       </c>
       <c r="M80" t="b">
         <v>1</v>
@@ -6115,7 +6115,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-04-20 08:39:49</t>
+          <t>2026-04-20 21:00:55</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6162,10 +6162,10 @@
         </is>
       </c>
       <c r="K81" t="n">
-        <v>168052</v>
+        <v>166985</v>
       </c>
       <c r="L81" t="n">
-        <v>114.17</v>
+        <v>113.54</v>
       </c>
       <c r="M81" t="b">
         <v>1</v>
@@ -6186,7 +6186,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-04-20 08:39:51</t>
+          <t>2026-04-20 21:00:57</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6233,10 +6233,10 @@
         </is>
       </c>
       <c r="K82" t="n">
-        <v>168052</v>
+        <v>166985</v>
       </c>
       <c r="L82" t="n">
-        <v>114.17</v>
+        <v>113.54</v>
       </c>
       <c r="M82" t="b">
         <v>1</v>
@@ -6257,7 +6257,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-04-20 08:39:51</t>
+          <t>2026-04-20 21:00:57</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6304,10 +6304,10 @@
         </is>
       </c>
       <c r="K83" t="n">
-        <v>168052</v>
+        <v>166985</v>
       </c>
       <c r="L83" t="n">
-        <v>114.17</v>
+        <v>113.54</v>
       </c>
       <c r="M83" t="b">
         <v>1</v>
@@ -6328,7 +6328,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-04-20 08:39:53</t>
+          <t>2026-04-20 21:00:59</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6375,10 +6375,10 @@
         </is>
       </c>
       <c r="K84" t="n">
-        <v>131386</v>
+        <v>130552</v>
       </c>
       <c r="L84" t="n">
-        <v>89.26000000000001</v>
+        <v>88.77</v>
       </c>
       <c r="M84" t="b">
         <v>1</v>
@@ -6399,7 +6399,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-04-20 08:39:53</t>
+          <t>2026-04-20 21:00:59</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6446,10 +6446,10 @@
         </is>
       </c>
       <c r="K85" t="n">
-        <v>131386</v>
+        <v>130552</v>
       </c>
       <c r="L85" t="n">
-        <v>89.26000000000001</v>
+        <v>88.77</v>
       </c>
       <c r="M85" t="b">
         <v>1</v>
@@ -6470,7 +6470,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-04-20 08:39:55</t>
+          <t>2026-04-20 21:01:01</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6517,10 +6517,10 @@
         </is>
       </c>
       <c r="K86" t="n">
-        <v>119164</v>
+        <v>118407</v>
       </c>
       <c r="L86" t="n">
-        <v>80.95999999999999</v>
+        <v>80.51000000000001</v>
       </c>
       <c r="M86" t="b">
         <v>1</v>
@@ -6541,7 +6541,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-04-20 08:39:55</t>
+          <t>2026-04-20 21:01:01</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -6588,10 +6588,10 @@
         </is>
       </c>
       <c r="K87" t="n">
-        <v>119164</v>
+        <v>118407</v>
       </c>
       <c r="L87" t="n">
-        <v>80.95999999999999</v>
+        <v>80.51000000000001</v>
       </c>
       <c r="M87" t="b">
         <v>1</v>
@@ -6612,7 +6612,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-04-20 08:39:56</t>
+          <t>2026-04-20 21:01:03</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -6659,10 +6659,10 @@
         </is>
       </c>
       <c r="K88" t="n">
-        <v>119164</v>
+        <v>118407</v>
       </c>
       <c r="L88" t="n">
-        <v>80.95999999999999</v>
+        <v>80.51000000000001</v>
       </c>
       <c r="M88" t="b">
         <v>1</v>
@@ -6683,7 +6683,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-04-20 08:39:56</t>
+          <t>2026-04-20 21:01:03</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -6730,10 +6730,10 @@
         </is>
       </c>
       <c r="K89" t="n">
-        <v>119164</v>
+        <v>118407</v>
       </c>
       <c r="L89" t="n">
-        <v>80.95999999999999</v>
+        <v>80.51000000000001</v>
       </c>
       <c r="M89" t="b">
         <v>1</v>
@@ -6754,7 +6754,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-04-20 08:39:58</t>
+          <t>2026-04-20 21:01:05</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -6801,10 +6801,10 @@
         </is>
       </c>
       <c r="K90" t="n">
-        <v>119164</v>
+        <v>118407</v>
       </c>
       <c r="L90" t="n">
-        <v>80.95999999999999</v>
+        <v>80.51000000000001</v>
       </c>
       <c r="M90" t="b">
         <v>1</v>
@@ -6825,7 +6825,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-04-20 08:39:58</t>
+          <t>2026-04-20 21:01:05</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -6872,10 +6872,10 @@
         </is>
       </c>
       <c r="K91" t="n">
-        <v>119164</v>
+        <v>118407</v>
       </c>
       <c r="L91" t="n">
-        <v>80.95999999999999</v>
+        <v>80.51000000000001</v>
       </c>
       <c r="M91" t="b">
         <v>1</v>
@@ -6896,7 +6896,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-04-20 08:40:00</t>
+          <t>2026-04-20 21:01:07</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6943,10 +6943,10 @@
         </is>
       </c>
       <c r="K92" t="n">
-        <v>119164</v>
+        <v>118407</v>
       </c>
       <c r="L92" t="n">
-        <v>80.95999999999999</v>
+        <v>80.51000000000001</v>
       </c>
       <c r="M92" t="b">
         <v>1</v>
@@ -6967,7 +6967,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-04-20 08:40:00</t>
+          <t>2026-04-20 21:01:07</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7014,10 +7014,10 @@
         </is>
       </c>
       <c r="K93" t="n">
-        <v>119164</v>
+        <v>118407</v>
       </c>
       <c r="L93" t="n">
-        <v>80.95999999999999</v>
+        <v>80.51000000000001</v>
       </c>
       <c r="M93" t="b">
         <v>1</v>
@@ -7038,7 +7038,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-04-20 08:40:02</t>
+          <t>2026-04-20 21:01:09</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7085,10 +7085,10 @@
         </is>
       </c>
       <c r="K94" t="n">
-        <v>198607</v>
+        <v>197346</v>
       </c>
       <c r="L94" t="n">
-        <v>134.93</v>
+        <v>134.19</v>
       </c>
       <c r="M94" t="b">
         <v>1</v>
@@ -7109,7 +7109,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-04-20 08:40:02</t>
+          <t>2026-04-20 21:01:09</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7156,10 +7156,10 @@
         </is>
       </c>
       <c r="K95" t="n">
-        <v>198607</v>
+        <v>197346</v>
       </c>
       <c r="L95" t="n">
-        <v>134.93</v>
+        <v>134.19</v>
       </c>
       <c r="M95" t="b">
         <v>1</v>
@@ -7180,7 +7180,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-04-20 08:40:04</t>
+          <t>2026-04-20 21:01:11</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7227,10 +7227,10 @@
         </is>
       </c>
       <c r="K96" t="n">
-        <v>216940</v>
+        <v>215563</v>
       </c>
       <c r="L96" t="n">
-        <v>147.38</v>
+        <v>146.57</v>
       </c>
       <c r="M96" t="b">
         <v>1</v>
@@ -7251,7 +7251,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-04-20 08:40:04</t>
+          <t>2026-04-20 21:01:11</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7298,10 +7298,10 @@
         </is>
       </c>
       <c r="K97" t="n">
-        <v>216940</v>
+        <v>215563</v>
       </c>
       <c r="L97" t="n">
-        <v>147.38</v>
+        <v>146.57</v>
       </c>
       <c r="M97" t="b">
         <v>1</v>
@@ -7322,7 +7322,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-04-20 08:40:06</t>
+          <t>2026-04-20 21:01:13</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -7369,10 +7369,10 @@
         </is>
       </c>
       <c r="K98" t="n">
-        <v>198607</v>
+        <v>197346</v>
       </c>
       <c r="L98" t="n">
-        <v>134.93</v>
+        <v>134.19</v>
       </c>
       <c r="M98" t="b">
         <v>1</v>
@@ -7393,7 +7393,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-04-20 08:40:06</t>
+          <t>2026-04-20 21:01:13</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -7440,10 +7440,10 @@
         </is>
       </c>
       <c r="K99" t="n">
-        <v>198607</v>
+        <v>197346</v>
       </c>
       <c r="L99" t="n">
-        <v>134.93</v>
+        <v>134.19</v>
       </c>
       <c r="M99" t="b">
         <v>1</v>
@@ -7464,7 +7464,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-04-20 08:40:08</t>
+          <t>2026-04-20 21:01:15</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -7511,10 +7511,10 @@
         </is>
       </c>
       <c r="K100" t="n">
-        <v>137497</v>
+        <v>136624</v>
       </c>
       <c r="L100" t="n">
-        <v>93.41</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="M100" t="b">
         <v>1</v>
@@ -7535,7 +7535,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-04-20 08:40:08</t>
+          <t>2026-04-20 21:01:15</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -7582,10 +7582,10 @@
         </is>
       </c>
       <c r="K101" t="n">
-        <v>137497</v>
+        <v>136624</v>
       </c>
       <c r="L101" t="n">
-        <v>93.41</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="M101" t="b">
         <v>1</v>
@@ -7606,7 +7606,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-04-20 08:40:10</t>
+          <t>2026-04-20 21:01:16</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -7653,10 +7653,10 @@
         </is>
       </c>
       <c r="K102" t="n">
-        <v>137497</v>
+        <v>136624</v>
       </c>
       <c r="L102" t="n">
-        <v>93.41</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="M102" t="b">
         <v>1</v>
@@ -7677,7 +7677,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-04-20 08:40:10</t>
+          <t>2026-04-20 21:01:16</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -7724,10 +7724,10 @@
         </is>
       </c>
       <c r="K103" t="n">
-        <v>137497</v>
+        <v>136624</v>
       </c>
       <c r="L103" t="n">
-        <v>93.41</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="M103" t="b">
         <v>1</v>
@@ -7748,7 +7748,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-04-20 08:40:11</t>
+          <t>2026-04-20 21:01:18</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -7795,10 +7795,10 @@
         </is>
       </c>
       <c r="K104" t="n">
-        <v>198607</v>
+        <v>197346</v>
       </c>
       <c r="L104" t="n">
-        <v>134.93</v>
+        <v>134.19</v>
       </c>
       <c r="M104" t="b">
         <v>1</v>
@@ -7819,7 +7819,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-04-20 08:40:11</t>
+          <t>2026-04-20 21:01:18</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -7866,10 +7866,10 @@
         </is>
       </c>
       <c r="K105" t="n">
-        <v>198607</v>
+        <v>197346</v>
       </c>
       <c r="L105" t="n">
-        <v>134.93</v>
+        <v>134.19</v>
       </c>
       <c r="M105" t="b">
         <v>1</v>
@@ -7890,7 +7890,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-04-20 08:40:13</t>
+          <t>2026-04-20 21:01:20</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -7937,10 +7937,10 @@
         </is>
       </c>
       <c r="K106" t="n">
-        <v>216940</v>
+        <v>215563</v>
       </c>
       <c r="L106" t="n">
-        <v>147.38</v>
+        <v>146.57</v>
       </c>
       <c r="M106" t="b">
         <v>1</v>
@@ -7961,7 +7961,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-04-20 08:40:13</t>
+          <t>2026-04-20 21:01:20</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8008,10 +8008,10 @@
         </is>
       </c>
       <c r="K107" t="n">
-        <v>216940</v>
+        <v>215563</v>
       </c>
       <c r="L107" t="n">
-        <v>147.38</v>
+        <v>146.57</v>
       </c>
       <c r="M107" t="b">
         <v>1</v>
@@ -8032,7 +8032,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-04-20 08:40:15</t>
+          <t>2026-04-20 21:01:22</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8079,10 +8079,10 @@
         </is>
       </c>
       <c r="K108" t="n">
-        <v>198607</v>
+        <v>197346</v>
       </c>
       <c r="L108" t="n">
-        <v>134.93</v>
+        <v>134.19</v>
       </c>
       <c r="M108" t="b">
         <v>1</v>
@@ -8103,7 +8103,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-04-20 08:40:15</t>
+          <t>2026-04-20 21:01:22</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8150,10 +8150,10 @@
         </is>
       </c>
       <c r="K109" t="n">
-        <v>198607</v>
+        <v>197346</v>
       </c>
       <c r="L109" t="n">
-        <v>134.93</v>
+        <v>134.19</v>
       </c>
       <c r="M109" t="b">
         <v>1</v>
@@ -8174,7 +8174,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-04-20 08:40:17</t>
+          <t>2026-04-20 21:01:24</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8221,10 +8221,10 @@
         </is>
       </c>
       <c r="K110" t="n">
-        <v>198607</v>
+        <v>197346</v>
       </c>
       <c r="L110" t="n">
-        <v>134.93</v>
+        <v>134.19</v>
       </c>
       <c r="M110" t="b">
         <v>1</v>
@@ -8245,7 +8245,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-04-20 08:40:17</t>
+          <t>2026-04-20 21:01:24</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -8292,10 +8292,10 @@
         </is>
       </c>
       <c r="K111" t="n">
-        <v>198607</v>
+        <v>197346</v>
       </c>
       <c r="L111" t="n">
-        <v>134.93</v>
+        <v>134.19</v>
       </c>
       <c r="M111" t="b">
         <v>1</v>
@@ -8316,7 +8316,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-04-20 08:40:19</t>
+          <t>2026-04-20 21:01:26</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -8363,10 +8363,10 @@
         </is>
       </c>
       <c r="K112" t="n">
-        <v>137497</v>
+        <v>136624</v>
       </c>
       <c r="L112" t="n">
-        <v>93.41</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="M112" t="b">
         <v>1</v>
@@ -8387,7 +8387,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-04-20 08:40:19</t>
+          <t>2026-04-20 21:01:26</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -8434,10 +8434,10 @@
         </is>
       </c>
       <c r="K113" t="n">
-        <v>137497</v>
+        <v>136624</v>
       </c>
       <c r="L113" t="n">
-        <v>93.41</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="M113" t="b">
         <v>1</v>
@@ -8458,7 +8458,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-04-20 08:40:21</t>
+          <t>2026-04-20 21:01:28</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -8505,10 +8505,10 @@
         </is>
       </c>
       <c r="K114" t="n">
-        <v>276293</v>
+        <v>276821</v>
       </c>
       <c r="L114" t="n">
-        <v>187.7</v>
+        <v>188.23</v>
       </c>
       <c r="M114" t="b">
         <v>1</v>
@@ -8529,7 +8529,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-04-20 08:40:21</t>
+          <t>2026-04-20 21:01:28</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -8576,10 +8576,10 @@
         </is>
       </c>
       <c r="K115" t="n">
-        <v>276293</v>
+        <v>276821</v>
       </c>
       <c r="L115" t="n">
-        <v>187.7</v>
+        <v>188.23</v>
       </c>
       <c r="M115" t="b">
         <v>1</v>
@@ -8600,7 +8600,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-04-20 08:40:23</t>
+          <t>2026-04-20 21:01:30</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -8647,10 +8647,10 @@
         </is>
       </c>
       <c r="K116" t="n">
-        <v>276293</v>
+        <v>276821</v>
       </c>
       <c r="L116" t="n">
-        <v>187.7</v>
+        <v>188.23</v>
       </c>
       <c r="M116" t="b">
         <v>1</v>
@@ -8671,7 +8671,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-04-20 08:40:23</t>
+          <t>2026-04-20 21:01:30</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -8718,10 +8718,10 @@
         </is>
       </c>
       <c r="K117" t="n">
-        <v>276293</v>
+        <v>276821</v>
       </c>
       <c r="L117" t="n">
-        <v>187.7</v>
+        <v>188.23</v>
       </c>
       <c r="M117" t="b">
         <v>1</v>
@@ -8742,7 +8742,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-04-20 08:40:25</t>
+          <t>2026-04-20 21:01:32</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -8789,10 +8789,10 @@
         </is>
       </c>
       <c r="K118" t="n">
-        <v>276293</v>
+        <v>276821</v>
       </c>
       <c r="L118" t="n">
-        <v>187.7</v>
+        <v>188.23</v>
       </c>
       <c r="M118" t="b">
         <v>1</v>
@@ -8813,7 +8813,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-04-20 08:40:25</t>
+          <t>2026-04-20 21:01:32</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -8860,10 +8860,10 @@
         </is>
       </c>
       <c r="K119" t="n">
-        <v>276293</v>
+        <v>276821</v>
       </c>
       <c r="L119" t="n">
-        <v>187.7</v>
+        <v>188.23</v>
       </c>
       <c r="M119" t="b">
         <v>1</v>
@@ -8884,7 +8884,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-04-20 08:40:27</t>
+          <t>2026-04-20 21:01:34</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -8931,10 +8931,10 @@
         </is>
       </c>
       <c r="K120" t="n">
-        <v>276293</v>
+        <v>276821</v>
       </c>
       <c r="L120" t="n">
-        <v>187.7</v>
+        <v>188.23</v>
       </c>
       <c r="M120" t="b">
         <v>1</v>
@@ -8955,7 +8955,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-04-20 08:40:27</t>
+          <t>2026-04-20 21:01:34</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9002,10 +9002,10 @@
         </is>
       </c>
       <c r="K121" t="n">
-        <v>276293</v>
+        <v>276821</v>
       </c>
       <c r="L121" t="n">
-        <v>187.7</v>
+        <v>188.23</v>
       </c>
       <c r="M121" t="b">
         <v>1</v>
@@ -9026,7 +9026,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-04-20 08:40:28</t>
+          <t>2026-04-20 21:01:36</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9073,10 +9073,10 @@
         </is>
       </c>
       <c r="K122" t="n">
-        <v>276293</v>
+        <v>276821</v>
       </c>
       <c r="L122" t="n">
-        <v>187.7</v>
+        <v>188.23</v>
       </c>
       <c r="M122" t="b">
         <v>1</v>
@@ -9097,7 +9097,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-04-20 08:40:28</t>
+          <t>2026-04-20 21:01:36</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9144,10 +9144,10 @@
         </is>
       </c>
       <c r="K123" t="n">
-        <v>276293</v>
+        <v>276821</v>
       </c>
       <c r="L123" t="n">
-        <v>187.7</v>
+        <v>188.23</v>
       </c>
       <c r="M123" t="b">
         <v>1</v>
@@ -9168,7 +9168,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-04-20 08:40:30</t>
+          <t>2026-04-20 21:01:37</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9215,10 +9215,10 @@
         </is>
       </c>
       <c r="K124" t="n">
-        <v>276293</v>
+        <v>276821</v>
       </c>
       <c r="L124" t="n">
-        <v>187.7</v>
+        <v>188.23</v>
       </c>
       <c r="M124" t="b">
         <v>1</v>
@@ -9239,7 +9239,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-04-20 08:40:30</t>
+          <t>2026-04-20 21:01:37</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -9286,10 +9286,10 @@
         </is>
       </c>
       <c r="K125" t="n">
-        <v>276293</v>
+        <v>276821</v>
       </c>
       <c r="L125" t="n">
-        <v>187.7</v>
+        <v>188.23</v>
       </c>
       <c r="M125" t="b">
         <v>1</v>
@@ -9310,7 +9310,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-04-20 08:40:33</t>
+          <t>2026-04-20 21:01:39</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -9357,10 +9357,10 @@
         </is>
       </c>
       <c r="K126" t="n">
-        <v>276293</v>
+        <v>276821</v>
       </c>
       <c r="L126" t="n">
-        <v>187.7</v>
+        <v>188.23</v>
       </c>
       <c r="M126" t="b">
         <v>1</v>
@@ -9381,7 +9381,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-04-20 08:40:33</t>
+          <t>2026-04-20 21:01:39</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -9428,10 +9428,10 @@
         </is>
       </c>
       <c r="K127" t="n">
-        <v>276293</v>
+        <v>276821</v>
       </c>
       <c r="L127" t="n">
-        <v>187.7</v>
+        <v>188.23</v>
       </c>
       <c r="M127" t="b">
         <v>1</v>
@@ -9452,7 +9452,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-04-20 08:40:34</t>
+          <t>2026-04-20 21:01:41</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -9499,10 +9499,10 @@
         </is>
       </c>
       <c r="K128" t="n">
-        <v>276293</v>
+        <v>276821</v>
       </c>
       <c r="L128" t="n">
-        <v>187.7</v>
+        <v>188.23</v>
       </c>
       <c r="M128" t="b">
         <v>1</v>
@@ -9523,7 +9523,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-04-20 08:40:34</t>
+          <t>2026-04-20 21:01:41</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -9570,10 +9570,10 @@
         </is>
       </c>
       <c r="K129" t="n">
-        <v>276293</v>
+        <v>276821</v>
       </c>
       <c r="L129" t="n">
-        <v>187.7</v>
+        <v>188.23</v>
       </c>
       <c r="M129" t="b">
         <v>1</v>
@@ -9594,7 +9594,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-04-20 08:40:36</t>
+          <t>2026-04-20 21:01:43</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -9641,10 +9641,10 @@
         </is>
       </c>
       <c r="K130" t="n">
-        <v>276293</v>
+        <v>276821</v>
       </c>
       <c r="L130" t="n">
-        <v>187.7</v>
+        <v>188.23</v>
       </c>
       <c r="M130" t="b">
         <v>1</v>
@@ -9665,7 +9665,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-04-20 08:40:36</t>
+          <t>2026-04-20 21:01:43</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -9712,10 +9712,10 @@
         </is>
       </c>
       <c r="K131" t="n">
-        <v>276293</v>
+        <v>276821</v>
       </c>
       <c r="L131" t="n">
-        <v>187.7</v>
+        <v>188.23</v>
       </c>
       <c r="M131" t="b">
         <v>1</v>
@@ -9736,7 +9736,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-04-20 08:40:38</t>
+          <t>2026-04-20 21:01:45</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -9783,10 +9783,10 @@
         </is>
       </c>
       <c r="K132" t="n">
-        <v>276293</v>
+        <v>276821</v>
       </c>
       <c r="L132" t="n">
-        <v>187.7</v>
+        <v>188.23</v>
       </c>
       <c r="M132" t="b">
         <v>1</v>
@@ -9807,7 +9807,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-04-20 08:40:38</t>
+          <t>2026-04-20 21:01:45</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -9854,10 +9854,10 @@
         </is>
       </c>
       <c r="K133" t="n">
-        <v>276293</v>
+        <v>276821</v>
       </c>
       <c r="L133" t="n">
-        <v>187.7</v>
+        <v>188.23</v>
       </c>
       <c r="M133" t="b">
         <v>1</v>
@@ -9878,7 +9878,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-04-20 08:40:40</t>
+          <t>2026-04-20 21:01:47</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -9925,10 +9925,10 @@
         </is>
       </c>
       <c r="K134" t="n">
-        <v>276293</v>
+        <v>276821</v>
       </c>
       <c r="L134" t="n">
-        <v>187.7</v>
+        <v>188.23</v>
       </c>
       <c r="M134" t="b">
         <v>1</v>
@@ -9949,7 +9949,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-04-20 08:40:40</t>
+          <t>2026-04-20 21:01:47</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="K135" t="n">
-        <v>276293</v>
+        <v>276821</v>
       </c>
       <c r="L135" t="n">
-        <v>187.7</v>
+        <v>188.23</v>
       </c>
       <c r="M135" t="b">
         <v>1</v>
@@ -10020,7 +10020,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-04-20 08:40:42</t>
+          <t>2026-04-20 21:01:49</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10067,10 +10067,10 @@
         </is>
       </c>
       <c r="K136" t="n">
-        <v>276293</v>
+        <v>276821</v>
       </c>
       <c r="L136" t="n">
-        <v>187.7</v>
+        <v>188.23</v>
       </c>
       <c r="M136" t="b">
         <v>1</v>
@@ -10091,7 +10091,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-04-20 08:40:42</t>
+          <t>2026-04-20 21:01:49</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10138,10 +10138,10 @@
         </is>
       </c>
       <c r="K137" t="n">
-        <v>276293</v>
+        <v>276821</v>
       </c>
       <c r="L137" t="n">
-        <v>187.7</v>
+        <v>188.23</v>
       </c>
       <c r="M137" t="b">
         <v>1</v>
@@ -10162,7 +10162,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-04-20 08:40:44</t>
+          <t>2026-04-20 21:01:51</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -10209,10 +10209,10 @@
         </is>
       </c>
       <c r="K138" t="n">
-        <v>276293</v>
+        <v>276821</v>
       </c>
       <c r="L138" t="n">
-        <v>187.7</v>
+        <v>188.23</v>
       </c>
       <c r="M138" t="b">
         <v>1</v>
@@ -10233,7 +10233,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-04-20 08:40:44</t>
+          <t>2026-04-20 21:01:51</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -10280,10 +10280,10 @@
         </is>
       </c>
       <c r="K139" t="n">
-        <v>276293</v>
+        <v>276821</v>
       </c>
       <c r="L139" t="n">
-        <v>187.7</v>
+        <v>188.23</v>
       </c>
       <c r="M139" t="b">
         <v>1</v>
@@ -10304,7 +10304,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-04-20 08:40:46</t>
+          <t>2026-04-20 21:01:53</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -10351,10 +10351,10 @@
         </is>
       </c>
       <c r="K140" t="n">
-        <v>276293</v>
+        <v>276821</v>
       </c>
       <c r="L140" t="n">
-        <v>187.7</v>
+        <v>188.23</v>
       </c>
       <c r="M140" t="b">
         <v>1</v>
@@ -10375,7 +10375,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-04-20 08:40:46</t>
+          <t>2026-04-20 21:01:53</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -10422,10 +10422,10 @@
         </is>
       </c>
       <c r="K141" t="n">
-        <v>276293</v>
+        <v>276821</v>
       </c>
       <c r="L141" t="n">
-        <v>187.7</v>
+        <v>188.23</v>
       </c>
       <c r="M141" t="b">
         <v>1</v>
@@ -10446,7 +10446,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-04-20 08:40:48</t>
+          <t>2026-04-20 21:01:55</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -10493,10 +10493,10 @@
         </is>
       </c>
       <c r="K142" t="n">
-        <v>291600</v>
+        <v>293100</v>
       </c>
       <c r="L142" t="n">
-        <v>198.1</v>
+        <v>199.29</v>
       </c>
       <c r="M142" t="b">
         <v>0</v>
@@ -10517,7 +10517,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-04-20 08:40:52</t>
+          <t>2026-04-20 21:01:57</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -10564,7 +10564,7 @@
         </is>
       </c>
       <c r="K143" t="n">
-        <v>301592</v>
+        <v>301329</v>
       </c>
       <c r="L143" t="n">
         <v>204.89</v>
@@ -10588,7 +10588,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-04-20 08:40:52</t>
+          <t>2026-04-20 21:01:57</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -10635,10 +10635,10 @@
         </is>
       </c>
       <c r="K144" t="n">
-        <v>171750</v>
+        <v>172077</v>
       </c>
       <c r="L144" t="n">
-        <v>116.68</v>
+        <v>117</v>
       </c>
       <c r="M144" t="b">
         <v>1</v>
@@ -10659,7 +10659,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-04-20 08:40:52</t>
+          <t>2026-04-20 21:01:57</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -10706,10 +10706,10 @@
         </is>
       </c>
       <c r="K145" t="n">
-        <v>171750</v>
+        <v>172077</v>
       </c>
       <c r="L145" t="n">
-        <v>116.68</v>
+        <v>117</v>
       </c>
       <c r="M145" t="b">
         <v>1</v>
@@ -10730,7 +10730,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-04-20 08:40:54</t>
+          <t>2026-04-20 21:01:59</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -10777,10 +10777,10 @@
         </is>
       </c>
       <c r="K146" t="n">
-        <v>171750</v>
+        <v>172077</v>
       </c>
       <c r="L146" t="n">
-        <v>116.68</v>
+        <v>117</v>
       </c>
       <c r="M146" t="b">
         <v>1</v>
@@ -10801,7 +10801,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-04-20 08:40:54</t>
+          <t>2026-04-20 21:01:59</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -10848,10 +10848,10 @@
         </is>
       </c>
       <c r="K147" t="n">
-        <v>171750</v>
+        <v>172077</v>
       </c>
       <c r="L147" t="n">
-        <v>116.68</v>
+        <v>117</v>
       </c>
       <c r="M147" t="b">
         <v>1</v>
@@ -10872,7 +10872,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-04-20 08:40:56</t>
+          <t>2026-04-20 21:02:01</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -10919,10 +10919,10 @@
         </is>
       </c>
       <c r="K148" t="n">
-        <v>171750</v>
+        <v>172077</v>
       </c>
       <c r="L148" t="n">
-        <v>116.68</v>
+        <v>117</v>
       </c>
       <c r="M148" t="b">
         <v>1</v>
@@ -10943,7 +10943,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-04-20 08:40:56</t>
+          <t>2026-04-20 21:02:01</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -10990,10 +10990,10 @@
         </is>
       </c>
       <c r="K149" t="n">
-        <v>171750</v>
+        <v>172077</v>
       </c>
       <c r="L149" t="n">
-        <v>116.68</v>
+        <v>117</v>
       </c>
       <c r="M149" t="b">
         <v>1</v>
@@ -11014,7 +11014,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-04-20 08:40:58</t>
+          <t>2026-04-20 21:02:03</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11061,10 +11061,10 @@
         </is>
       </c>
       <c r="K150" t="n">
-        <v>171750</v>
+        <v>172077</v>
       </c>
       <c r="L150" t="n">
-        <v>116.68</v>
+        <v>117</v>
       </c>
       <c r="M150" t="b">
         <v>1</v>
@@ -11085,7 +11085,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026-04-20 08:40:58</t>
+          <t>2026-04-20 21:02:03</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11132,10 +11132,10 @@
         </is>
       </c>
       <c r="K151" t="n">
-        <v>171750</v>
+        <v>172077</v>
       </c>
       <c r="L151" t="n">
-        <v>116.68</v>
+        <v>117</v>
       </c>
       <c r="M151" t="b">
         <v>1</v>
@@ -11156,7 +11156,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2026-04-20 08:41:00</t>
+          <t>2026-04-20 21:02:05</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -11203,10 +11203,10 @@
         </is>
       </c>
       <c r="K152" t="n">
-        <v>171750</v>
+        <v>172077</v>
       </c>
       <c r="L152" t="n">
-        <v>116.68</v>
+        <v>117</v>
       </c>
       <c r="M152" t="b">
         <v>1</v>
@@ -11227,7 +11227,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2026-04-20 08:41:00</t>
+          <t>2026-04-20 21:02:05</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -11274,10 +11274,10 @@
         </is>
       </c>
       <c r="K153" t="n">
-        <v>171750</v>
+        <v>172077</v>
       </c>
       <c r="L153" t="n">
-        <v>116.68</v>
+        <v>117</v>
       </c>
       <c r="M153" t="b">
         <v>1</v>
@@ -11298,7 +11298,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2026-04-20 08:41:01</t>
+          <t>2026-04-20 21:02:06</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -11345,10 +11345,10 @@
         </is>
       </c>
       <c r="K154" t="n">
-        <v>171750</v>
+        <v>172077</v>
       </c>
       <c r="L154" t="n">
-        <v>116.68</v>
+        <v>117</v>
       </c>
       <c r="M154" t="b">
         <v>1</v>
@@ -11369,7 +11369,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2026-04-20 08:41:01</t>
+          <t>2026-04-20 21:02:06</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -11416,10 +11416,10 @@
         </is>
       </c>
       <c r="K155" t="n">
-        <v>171750</v>
+        <v>172077</v>
       </c>
       <c r="L155" t="n">
-        <v>116.68</v>
+        <v>117</v>
       </c>
       <c r="M155" t="b">
         <v>1</v>
@@ -11440,7 +11440,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2026-04-20 08:41:03</t>
+          <t>2026-04-20 21:02:08</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -11487,10 +11487,10 @@
         </is>
       </c>
       <c r="K156" t="n">
-        <v>171750</v>
+        <v>172077</v>
       </c>
       <c r="L156" t="n">
-        <v>116.68</v>
+        <v>117</v>
       </c>
       <c r="M156" t="b">
         <v>1</v>
@@ -11511,7 +11511,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2026-04-20 08:41:03</t>
+          <t>2026-04-20 21:02:08</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -11558,10 +11558,10 @@
         </is>
       </c>
       <c r="K157" t="n">
-        <v>171750</v>
+        <v>172077</v>
       </c>
       <c r="L157" t="n">
-        <v>116.68</v>
+        <v>117</v>
       </c>
       <c r="M157" t="b">
         <v>1</v>
@@ -11582,7 +11582,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2026-04-20 08:41:05</t>
+          <t>2026-04-20 21:02:10</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -11629,10 +11629,10 @@
         </is>
       </c>
       <c r="K158" t="n">
-        <v>171750</v>
+        <v>172077</v>
       </c>
       <c r="L158" t="n">
-        <v>116.68</v>
+        <v>117</v>
       </c>
       <c r="M158" t="b">
         <v>1</v>
@@ -11653,7 +11653,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2026-04-20 08:41:05</t>
+          <t>2026-04-20 21:02:10</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -11700,10 +11700,10 @@
         </is>
       </c>
       <c r="K159" t="n">
-        <v>171750</v>
+        <v>172077</v>
       </c>
       <c r="L159" t="n">
-        <v>116.68</v>
+        <v>117</v>
       </c>
       <c r="M159" t="b">
         <v>1</v>
@@ -11724,7 +11724,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2026-04-20 08:41:07</t>
+          <t>2026-04-20 21:02:12</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -11771,10 +11771,10 @@
         </is>
       </c>
       <c r="K160" t="n">
-        <v>171750</v>
+        <v>172077</v>
       </c>
       <c r="L160" t="n">
-        <v>116.68</v>
+        <v>117</v>
       </c>
       <c r="M160" t="b">
         <v>1</v>
@@ -11795,7 +11795,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2026-04-20 08:41:07</t>
+          <t>2026-04-20 21:02:12</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -11842,10 +11842,10 @@
         </is>
       </c>
       <c r="K161" t="n">
-        <v>171750</v>
+        <v>172077</v>
       </c>
       <c r="L161" t="n">
-        <v>116.68</v>
+        <v>117</v>
       </c>
       <c r="M161" t="b">
         <v>1</v>
@@ -11866,7 +11866,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2026-04-20 08:41:09</t>
+          <t>2026-04-20 21:02:14</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -11913,10 +11913,10 @@
         </is>
       </c>
       <c r="K162" t="n">
-        <v>171750</v>
+        <v>172077</v>
       </c>
       <c r="L162" t="n">
-        <v>116.68</v>
+        <v>117</v>
       </c>
       <c r="M162" t="b">
         <v>1</v>
@@ -11937,7 +11937,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2026-04-20 08:41:09</t>
+          <t>2026-04-20 21:02:14</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -11984,10 +11984,10 @@
         </is>
       </c>
       <c r="K163" t="n">
-        <v>171750</v>
+        <v>172077</v>
       </c>
       <c r="L163" t="n">
-        <v>116.68</v>
+        <v>117</v>
       </c>
       <c r="M163" t="b">
         <v>1</v>
@@ -12008,7 +12008,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2026-04-20 08:41:11</t>
+          <t>2026-04-20 21:02:16</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -12055,10 +12055,10 @@
         </is>
       </c>
       <c r="K164" t="n">
-        <v>171750</v>
+        <v>172077</v>
       </c>
       <c r="L164" t="n">
-        <v>116.68</v>
+        <v>117</v>
       </c>
       <c r="M164" t="b">
         <v>1</v>
@@ -12079,7 +12079,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2026-04-20 08:41:11</t>
+          <t>2026-04-20 21:02:16</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -12126,10 +12126,10 @@
         </is>
       </c>
       <c r="K165" t="n">
-        <v>171750</v>
+        <v>172077</v>
       </c>
       <c r="L165" t="n">
-        <v>116.68</v>
+        <v>117</v>
       </c>
       <c r="M165" t="b">
         <v>1</v>
@@ -12150,7 +12150,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2026-04-20 08:41:13</t>
+          <t>2026-04-20 21:02:18</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -12197,10 +12197,10 @@
         </is>
       </c>
       <c r="K166" t="n">
-        <v>171750</v>
+        <v>172077</v>
       </c>
       <c r="L166" t="n">
-        <v>116.68</v>
+        <v>117</v>
       </c>
       <c r="M166" t="b">
         <v>1</v>
@@ -12221,7 +12221,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2026-04-20 08:41:13</t>
+          <t>2026-04-20 21:02:18</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -12268,10 +12268,10 @@
         </is>
       </c>
       <c r="K167" t="n">
-        <v>171750</v>
+        <v>172077</v>
       </c>
       <c r="L167" t="n">
-        <v>116.68</v>
+        <v>117</v>
       </c>
       <c r="M167" t="b">
         <v>1</v>
@@ -12292,7 +12292,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2026-04-20 08:41:15</t>
+          <t>2026-04-20 21:02:20</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -12339,10 +12339,10 @@
         </is>
       </c>
       <c r="K168" t="n">
-        <v>171750</v>
+        <v>172077</v>
       </c>
       <c r="L168" t="n">
-        <v>116.68</v>
+        <v>117</v>
       </c>
       <c r="M168" t="b">
         <v>1</v>
@@ -12363,7 +12363,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2026-04-20 08:41:15</t>
+          <t>2026-04-20 21:02:20</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -12410,10 +12410,10 @@
         </is>
       </c>
       <c r="K169" t="n">
-        <v>171750</v>
+        <v>172077</v>
       </c>
       <c r="L169" t="n">
-        <v>116.68</v>
+        <v>117</v>
       </c>
       <c r="M169" t="b">
         <v>1</v>
@@ -12434,7 +12434,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2026-04-20 08:41:17</t>
+          <t>2026-04-20 21:02:22</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -12481,10 +12481,10 @@
         </is>
       </c>
       <c r="K170" t="n">
-        <v>171750</v>
+        <v>172077</v>
       </c>
       <c r="L170" t="n">
-        <v>116.68</v>
+        <v>117</v>
       </c>
       <c r="M170" t="b">
         <v>1</v>
@@ -12505,7 +12505,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2026-04-20 08:41:17</t>
+          <t>2026-04-20 21:02:22</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -12552,10 +12552,10 @@
         </is>
       </c>
       <c r="K171" t="n">
-        <v>171750</v>
+        <v>172077</v>
       </c>
       <c r="L171" t="n">
-        <v>116.68</v>
+        <v>117</v>
       </c>
       <c r="M171" t="b">
         <v>1</v>
@@ -12576,7 +12576,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2026-04-20 08:41:18</t>
+          <t>2026-04-20 21:02:24</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -12623,10 +12623,10 @@
         </is>
       </c>
       <c r="K172" t="n">
-        <v>203300</v>
+        <v>204300</v>
       </c>
       <c r="L172" t="n">
-        <v>138.11</v>
+        <v>138.91</v>
       </c>
       <c r="M172" t="b">
         <v>0</v>
@@ -12647,7 +12647,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2026-04-20 08:41:19</t>
+          <t>2026-04-20 21:02:24</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -12694,10 +12694,10 @@
         </is>
       </c>
       <c r="K173" t="n">
-        <v>167269</v>
+        <v>167588</v>
       </c>
       <c r="L173" t="n">
-        <v>113.64</v>
+        <v>113.95</v>
       </c>
       <c r="M173" t="b">
         <v>1</v>
@@ -12718,7 +12718,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2026-04-20 08:41:19</t>
+          <t>2026-04-20 21:02:24</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -12765,10 +12765,10 @@
         </is>
       </c>
       <c r="K174" t="n">
-        <v>167269</v>
+        <v>167588</v>
       </c>
       <c r="L174" t="n">
-        <v>113.64</v>
+        <v>113.95</v>
       </c>
       <c r="M174" t="b">
         <v>1</v>
@@ -12789,7 +12789,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2026-04-20 08:41:20</t>
+          <t>2026-04-20 21:02:26</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -12836,10 +12836,10 @@
         </is>
       </c>
       <c r="K175" t="n">
-        <v>167269</v>
+        <v>167588</v>
       </c>
       <c r="L175" t="n">
-        <v>113.64</v>
+        <v>113.95</v>
       </c>
       <c r="M175" t="b">
         <v>1</v>
@@ -12860,7 +12860,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2026-04-20 08:41:20</t>
+          <t>2026-04-20 21:02:26</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -12907,10 +12907,10 @@
         </is>
       </c>
       <c r="K176" t="n">
-        <v>167269</v>
+        <v>167588</v>
       </c>
       <c r="L176" t="n">
-        <v>113.64</v>
+        <v>113.95</v>
       </c>
       <c r="M176" t="b">
         <v>1</v>
@@ -12931,7 +12931,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2026-04-20 08:41:22</t>
+          <t>2026-04-20 21:02:28</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -12978,10 +12978,10 @@
         </is>
       </c>
       <c r="K177" t="n">
-        <v>167269</v>
+        <v>167588</v>
       </c>
       <c r="L177" t="n">
-        <v>113.64</v>
+        <v>113.95</v>
       </c>
       <c r="M177" t="b">
         <v>1</v>
@@ -13002,7 +13002,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2026-04-20 08:41:22</t>
+          <t>2026-04-20 21:02:28</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -13049,10 +13049,10 @@
         </is>
       </c>
       <c r="K178" t="n">
-        <v>167269</v>
+        <v>167588</v>
       </c>
       <c r="L178" t="n">
-        <v>113.64</v>
+        <v>113.95</v>
       </c>
       <c r="M178" t="b">
         <v>1</v>
@@ -13073,7 +13073,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2026-04-20 08:41:24</t>
+          <t>2026-04-20 21:02:29</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -13120,10 +13120,10 @@
         </is>
       </c>
       <c r="K179" t="n">
-        <v>167269</v>
+        <v>167588</v>
       </c>
       <c r="L179" t="n">
-        <v>113.64</v>
+        <v>113.95</v>
       </c>
       <c r="M179" t="b">
         <v>1</v>
@@ -13144,7 +13144,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2026-04-20 08:41:24</t>
+          <t>2026-04-20 21:02:29</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -13191,10 +13191,10 @@
         </is>
       </c>
       <c r="K180" t="n">
-        <v>167269</v>
+        <v>167588</v>
       </c>
       <c r="L180" t="n">
-        <v>113.64</v>
+        <v>113.95</v>
       </c>
       <c r="M180" t="b">
         <v>1</v>
@@ -13215,7 +13215,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2026-04-20 08:41:26</t>
+          <t>2026-04-20 21:02:31</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -13262,10 +13262,10 @@
         </is>
       </c>
       <c r="K181" t="n">
-        <v>167269</v>
+        <v>167588</v>
       </c>
       <c r="L181" t="n">
-        <v>113.64</v>
+        <v>113.95</v>
       </c>
       <c r="M181" t="b">
         <v>1</v>
@@ -13286,7 +13286,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2026-04-20 08:41:26</t>
+          <t>2026-04-20 21:02:31</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -13333,10 +13333,10 @@
         </is>
       </c>
       <c r="K182" t="n">
-        <v>167269</v>
+        <v>167588</v>
       </c>
       <c r="L182" t="n">
-        <v>113.64</v>
+        <v>113.95</v>
       </c>
       <c r="M182" t="b">
         <v>1</v>
@@ -13357,7 +13357,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2026-04-20 08:41:28</t>
+          <t>2026-04-20 21:02:33</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -13404,10 +13404,10 @@
         </is>
       </c>
       <c r="K183" t="n">
-        <v>167269</v>
+        <v>167588</v>
       </c>
       <c r="L183" t="n">
-        <v>113.64</v>
+        <v>113.95</v>
       </c>
       <c r="M183" t="b">
         <v>1</v>
@@ -13428,7 +13428,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2026-04-20 08:41:28</t>
+          <t>2026-04-20 21:02:33</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -13475,10 +13475,10 @@
         </is>
       </c>
       <c r="K184" t="n">
-        <v>167269</v>
+        <v>167588</v>
       </c>
       <c r="L184" t="n">
-        <v>113.64</v>
+        <v>113.95</v>
       </c>
       <c r="M184" t="b">
         <v>1</v>
@@ -13499,7 +13499,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2026-04-20 08:41:30</t>
+          <t>2026-04-20 21:02:35</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -13546,10 +13546,10 @@
         </is>
       </c>
       <c r="K185" t="n">
-        <v>167269</v>
+        <v>167588</v>
       </c>
       <c r="L185" t="n">
-        <v>113.64</v>
+        <v>113.95</v>
       </c>
       <c r="M185" t="b">
         <v>1</v>
@@ -13570,7 +13570,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2026-04-20 08:41:30</t>
+          <t>2026-04-20 21:02:35</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -13617,10 +13617,10 @@
         </is>
       </c>
       <c r="K186" t="n">
-        <v>167269</v>
+        <v>167588</v>
       </c>
       <c r="L186" t="n">
-        <v>113.64</v>
+        <v>113.95</v>
       </c>
       <c r="M186" t="b">
         <v>1</v>
@@ -13641,7 +13641,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2026-04-20 08:41:31</t>
+          <t>2026-04-20 21:02:37</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -13688,10 +13688,10 @@
         </is>
       </c>
       <c r="K187" t="n">
-        <v>167269</v>
+        <v>167588</v>
       </c>
       <c r="L187" t="n">
-        <v>113.64</v>
+        <v>113.95</v>
       </c>
       <c r="M187" t="b">
         <v>1</v>
@@ -13712,7 +13712,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2026-04-20 08:41:31</t>
+          <t>2026-04-20 21:02:37</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -13759,10 +13759,10 @@
         </is>
       </c>
       <c r="K188" t="n">
-        <v>167269</v>
+        <v>167588</v>
       </c>
       <c r="L188" t="n">
-        <v>113.64</v>
+        <v>113.95</v>
       </c>
       <c r="M188" t="b">
         <v>1</v>
@@ -13783,7 +13783,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2026-04-20 08:41:33</t>
+          <t>2026-04-20 21:02:39</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -13830,10 +13830,10 @@
         </is>
       </c>
       <c r="K189" t="n">
-        <v>167269</v>
+        <v>167588</v>
       </c>
       <c r="L189" t="n">
-        <v>113.64</v>
+        <v>113.95</v>
       </c>
       <c r="M189" t="b">
         <v>1</v>
@@ -13854,7 +13854,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2026-04-20 08:41:33</t>
+          <t>2026-04-20 21:02:39</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -13901,10 +13901,10 @@
         </is>
       </c>
       <c r="K190" t="n">
-        <v>167269</v>
+        <v>167588</v>
       </c>
       <c r="L190" t="n">
-        <v>113.64</v>
+        <v>113.95</v>
       </c>
       <c r="M190" t="b">
         <v>1</v>
@@ -13925,7 +13925,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2026-04-20 08:41:35</t>
+          <t>2026-04-20 21:02:41</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -13972,10 +13972,10 @@
         </is>
       </c>
       <c r="K191" t="n">
-        <v>167269</v>
+        <v>167588</v>
       </c>
       <c r="L191" t="n">
-        <v>113.64</v>
+        <v>113.95</v>
       </c>
       <c r="M191" t="b">
         <v>1</v>
@@ -13996,7 +13996,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2026-04-20 08:41:35</t>
+          <t>2026-04-20 21:02:41</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -14043,10 +14043,10 @@
         </is>
       </c>
       <c r="K192" t="n">
-        <v>167269</v>
+        <v>167588</v>
       </c>
       <c r="L192" t="n">
-        <v>113.64</v>
+        <v>113.95</v>
       </c>
       <c r="M192" t="b">
         <v>1</v>
@@ -14067,7 +14067,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2026-04-20 08:41:37</t>
+          <t>2026-04-20 21:02:43</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -14114,10 +14114,10 @@
         </is>
       </c>
       <c r="K193" t="n">
-        <v>167269</v>
+        <v>167588</v>
       </c>
       <c r="L193" t="n">
-        <v>113.64</v>
+        <v>113.95</v>
       </c>
       <c r="M193" t="b">
         <v>1</v>
@@ -14138,7 +14138,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2026-04-20 08:41:37</t>
+          <t>2026-04-20 21:02:43</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -14185,10 +14185,10 @@
         </is>
       </c>
       <c r="K194" t="n">
-        <v>167269</v>
+        <v>167588</v>
       </c>
       <c r="L194" t="n">
-        <v>113.64</v>
+        <v>113.95</v>
       </c>
       <c r="M194" t="b">
         <v>1</v>
@@ -14209,7 +14209,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2026-04-20 08:41:39</t>
+          <t>2026-04-20 21:02:45</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -14256,10 +14256,10 @@
         </is>
       </c>
       <c r="K195" t="n">
-        <v>167269</v>
+        <v>167588</v>
       </c>
       <c r="L195" t="n">
-        <v>113.64</v>
+        <v>113.95</v>
       </c>
       <c r="M195" t="b">
         <v>1</v>
@@ -14280,7 +14280,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2026-04-20 08:41:39</t>
+          <t>2026-04-20 21:02:45</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -14327,10 +14327,10 @@
         </is>
       </c>
       <c r="K196" t="n">
-        <v>167269</v>
+        <v>167588</v>
       </c>
       <c r="L196" t="n">
-        <v>113.64</v>
+        <v>113.95</v>
       </c>
       <c r="M196" t="b">
         <v>1</v>
@@ -14351,7 +14351,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2026-04-20 08:41:41</t>
+          <t>2026-04-20 21:02:46</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -14398,10 +14398,10 @@
         </is>
       </c>
       <c r="K197" t="n">
-        <v>167269</v>
+        <v>167588</v>
       </c>
       <c r="L197" t="n">
-        <v>113.64</v>
+        <v>113.95</v>
       </c>
       <c r="M197" t="b">
         <v>1</v>
@@ -14422,7 +14422,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2026-04-20 08:41:41</t>
+          <t>2026-04-20 21:02:46</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -14469,10 +14469,10 @@
         </is>
       </c>
       <c r="K198" t="n">
-        <v>167269</v>
+        <v>167588</v>
       </c>
       <c r="L198" t="n">
-        <v>113.64</v>
+        <v>113.95</v>
       </c>
       <c r="M198" t="b">
         <v>1</v>
@@ -14493,7 +14493,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2026-04-20 08:41:43</t>
+          <t>2026-04-20 21:02:48</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -14540,10 +14540,10 @@
         </is>
       </c>
       <c r="K199" t="n">
-        <v>167269</v>
+        <v>167588</v>
       </c>
       <c r="L199" t="n">
-        <v>113.64</v>
+        <v>113.95</v>
       </c>
       <c r="M199" t="b">
         <v>1</v>
@@ -14564,7 +14564,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2026-04-20 08:41:43</t>
+          <t>2026-04-20 21:02:48</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -14611,10 +14611,10 @@
         </is>
       </c>
       <c r="K200" t="n">
-        <v>167269</v>
+        <v>167588</v>
       </c>
       <c r="L200" t="n">
-        <v>113.64</v>
+        <v>113.95</v>
       </c>
       <c r="M200" t="b">
         <v>1</v>
@@ -14635,7 +14635,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2026-04-20 08:41:44</t>
+          <t>2026-04-20 21:02:50</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -14698,7 +14698,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>2026-04-20 08:41:45</t>
+          <t>2026-04-20 21:02:51</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -14761,7 +14761,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2026-04-20 08:41:45</t>
+          <t>2026-04-20 21:02:51</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -14824,7 +14824,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2026-04-20 08:41:47</t>
+          <t>2026-04-20 21:02:53</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -14887,7 +14887,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2026-04-20 08:41:49</t>
+          <t>2026-04-20 21:02:55</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -14950,7 +14950,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2026-04-20 08:41:51</t>
+          <t>2026-04-20 21:02:57</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -15013,7 +15013,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2026-04-20 08:41:53</t>
+          <t>2026-04-20 21:02:59</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -15076,7 +15076,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2026-04-20 08:41:55</t>
+          <t>2026-04-20 21:03:00</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -15139,7 +15139,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>2026-04-20 08:41:56</t>
+          <t>2026-04-20 21:03:02</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -15202,7 +15202,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2026-04-20 08:41:58</t>
+          <t>2026-04-20 21:03:04</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -15265,7 +15265,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2026-04-20 08:42:00</t>
+          <t>2026-04-20 21:03:06</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -15328,7 +15328,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>2026-04-20 08:42:02</t>
+          <t>2026-04-20 21:03:08</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -15391,7 +15391,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2026-04-20 08:42:04</t>
+          <t>2026-04-20 21:03:10</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -15454,7 +15454,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>2026-04-20 08:42:05</t>
+          <t>2026-04-20 21:03:12</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -15517,7 +15517,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>2026-04-20 08:42:07</t>
+          <t>2026-04-20 21:03:14</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -15580,7 +15580,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2026-04-20 08:42:09</t>
+          <t>2026-04-20 21:03:16</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -15643,7 +15643,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>2026-04-20 08:42:11</t>
+          <t>2026-04-20 21:03:17</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -15706,7 +15706,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>2026-04-20 08:42:11</t>
+          <t>2026-04-20 21:03:17</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -15753,10 +15753,10 @@
         </is>
       </c>
       <c r="K218" t="n">
-        <v>216554</v>
+        <v>216967</v>
       </c>
       <c r="L218" t="n">
-        <v>147.12</v>
+        <v>147.53</v>
       </c>
       <c r="M218" t="b">
         <v>0</v>
@@ -15777,7 +15777,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>2026-04-20 08:42:11</t>
+          <t>2026-04-20 21:03:17</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -15824,10 +15824,10 @@
         </is>
       </c>
       <c r="K219" t="n">
-        <v>216554</v>
+        <v>216967</v>
       </c>
       <c r="L219" t="n">
-        <v>147.12</v>
+        <v>147.53</v>
       </c>
       <c r="M219" t="b">
         <v>0</v>
@@ -15848,7 +15848,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>2026-04-20 08:42:13</t>
+          <t>2026-04-20 21:03:19</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -15895,10 +15895,10 @@
         </is>
       </c>
       <c r="K220" t="n">
-        <v>216554</v>
+        <v>216967</v>
       </c>
       <c r="L220" t="n">
-        <v>147.12</v>
+        <v>147.53</v>
       </c>
       <c r="M220" t="b">
         <v>0</v>
@@ -15919,7 +15919,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>2026-04-20 08:42:13</t>
+          <t>2026-04-20 21:03:19</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -15966,10 +15966,10 @@
         </is>
       </c>
       <c r="K221" t="n">
-        <v>216554</v>
+        <v>216967</v>
       </c>
       <c r="L221" t="n">
-        <v>147.12</v>
+        <v>147.53</v>
       </c>
       <c r="M221" t="b">
         <v>0</v>
@@ -15990,7 +15990,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>2026-04-20 08:42:15</t>
+          <t>2026-04-20 21:03:21</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -16037,10 +16037,10 @@
         </is>
       </c>
       <c r="K222" t="n">
-        <v>216554</v>
+        <v>216967</v>
       </c>
       <c r="L222" t="n">
-        <v>147.12</v>
+        <v>147.53</v>
       </c>
       <c r="M222" t="b">
         <v>0</v>
@@ -16061,7 +16061,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>2026-04-20 08:42:15</t>
+          <t>2026-04-20 21:03:21</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -16108,10 +16108,10 @@
         </is>
       </c>
       <c r="K223" t="n">
-        <v>216554</v>
+        <v>216967</v>
       </c>
       <c r="L223" t="n">
-        <v>147.12</v>
+        <v>147.53</v>
       </c>
       <c r="M223" t="b">
         <v>0</v>
@@ -16132,7 +16132,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>2026-04-20 08:42:17</t>
+          <t>2026-04-20 21:03:23</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -16179,10 +16179,10 @@
         </is>
       </c>
       <c r="K224" t="n">
-        <v>216554</v>
+        <v>216967</v>
       </c>
       <c r="L224" t="n">
-        <v>147.12</v>
+        <v>147.53</v>
       </c>
       <c r="M224" t="b">
         <v>0</v>
@@ -16203,7 +16203,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>2026-04-20 08:42:17</t>
+          <t>2026-04-20 21:03:23</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -16250,10 +16250,10 @@
         </is>
       </c>
       <c r="K225" t="n">
-        <v>216554</v>
+        <v>216967</v>
       </c>
       <c r="L225" t="n">
-        <v>147.12</v>
+        <v>147.53</v>
       </c>
       <c r="M225" t="b">
         <v>0</v>
@@ -16274,7 +16274,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>2026-04-20 08:42:19</t>
+          <t>2026-04-20 21:03:25</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -16321,10 +16321,10 @@
         </is>
       </c>
       <c r="K226" t="n">
-        <v>216554</v>
+        <v>216967</v>
       </c>
       <c r="L226" t="n">
-        <v>147.12</v>
+        <v>147.53</v>
       </c>
       <c r="M226" t="b">
         <v>0</v>
@@ -16345,7 +16345,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>2026-04-20 08:42:20</t>
+          <t>2026-04-20 21:03:27</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -16392,10 +16392,10 @@
         </is>
       </c>
       <c r="K227" t="n">
-        <v>216554</v>
+        <v>216967</v>
       </c>
       <c r="L227" t="n">
-        <v>147.12</v>
+        <v>147.53</v>
       </c>
       <c r="M227" t="b">
         <v>0</v>
@@ -16416,7 +16416,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>2026-04-20 08:42:23</t>
+          <t>2026-04-20 21:03:29</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -16463,10 +16463,10 @@
         </is>
       </c>
       <c r="K228" t="n">
-        <v>216554</v>
+        <v>216967</v>
       </c>
       <c r="L228" t="n">
-        <v>147.12</v>
+        <v>147.53</v>
       </c>
       <c r="M228" t="b">
         <v>0</v>
@@ -16487,7 +16487,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>2026-04-20 08:42:23</t>
+          <t>2026-04-20 21:03:29</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -16534,10 +16534,10 @@
         </is>
       </c>
       <c r="K229" t="n">
-        <v>216554</v>
+        <v>216967</v>
       </c>
       <c r="L229" t="n">
-        <v>147.12</v>
+        <v>147.53</v>
       </c>
       <c r="M229" t="b">
         <v>0</v>
@@ -16558,7 +16558,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>2026-04-20 08:42:24</t>
+          <t>2026-04-20 21:03:31</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -16605,10 +16605,10 @@
         </is>
       </c>
       <c r="K230" t="n">
-        <v>216554</v>
+        <v>216967</v>
       </c>
       <c r="L230" t="n">
-        <v>147.12</v>
+        <v>147.53</v>
       </c>
       <c r="M230" t="b">
         <v>0</v>
@@ -16629,7 +16629,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>2026-04-20 08:42:24</t>
+          <t>2026-04-20 21:03:31</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -16676,10 +16676,10 @@
         </is>
       </c>
       <c r="K231" t="n">
-        <v>216554</v>
+        <v>216967</v>
       </c>
       <c r="L231" t="n">
-        <v>147.12</v>
+        <v>147.53</v>
       </c>
       <c r="M231" t="b">
         <v>0</v>
@@ -16700,7 +16700,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>2026-04-20 08:42:26</t>
+          <t>2026-04-20 21:03:33</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -16747,10 +16747,10 @@
         </is>
       </c>
       <c r="K232" t="n">
-        <v>216554</v>
+        <v>216967</v>
       </c>
       <c r="L232" t="n">
-        <v>147.12</v>
+        <v>147.53</v>
       </c>
       <c r="M232" t="b">
         <v>0</v>
@@ -16771,7 +16771,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>2026-04-20 08:42:26</t>
+          <t>2026-04-20 21:03:33</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -16818,10 +16818,10 @@
         </is>
       </c>
       <c r="K233" t="n">
-        <v>216554</v>
+        <v>216967</v>
       </c>
       <c r="L233" t="n">
-        <v>147.12</v>
+        <v>147.53</v>
       </c>
       <c r="M233" t="b">
         <v>0</v>
@@ -16842,7 +16842,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>2026-04-20 08:42:28</t>
+          <t>2026-04-20 21:03:35</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -16889,10 +16889,10 @@
         </is>
       </c>
       <c r="K234" t="n">
-        <v>216554</v>
+        <v>216967</v>
       </c>
       <c r="L234" t="n">
-        <v>147.12</v>
+        <v>147.53</v>
       </c>
       <c r="M234" t="b">
         <v>0</v>
@@ -16913,7 +16913,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>2026-04-20 08:42:28</t>
+          <t>2026-04-20 21:03:35</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -16960,10 +16960,10 @@
         </is>
       </c>
       <c r="K235" t="n">
-        <v>216554</v>
+        <v>216967</v>
       </c>
       <c r="L235" t="n">
-        <v>147.12</v>
+        <v>147.53</v>
       </c>
       <c r="M235" t="b">
         <v>0</v>
@@ -16984,7 +16984,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>2026-04-20 08:42:30</t>
+          <t>2026-04-20 21:03:37</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -17031,10 +17031,10 @@
         </is>
       </c>
       <c r="K236" t="n">
-        <v>216554</v>
+        <v>216967</v>
       </c>
       <c r="L236" t="n">
-        <v>147.12</v>
+        <v>147.53</v>
       </c>
       <c r="M236" t="b">
         <v>0</v>
@@ -17055,7 +17055,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>2026-04-20 08:42:30</t>
+          <t>2026-04-20 21:03:37</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -17102,10 +17102,10 @@
         </is>
       </c>
       <c r="K237" t="n">
-        <v>216554</v>
+        <v>216967</v>
       </c>
       <c r="L237" t="n">
-        <v>147.12</v>
+        <v>147.53</v>
       </c>
       <c r="M237" t="b">
         <v>0</v>
@@ -17126,7 +17126,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>2026-04-20 08:42:32</t>
+          <t>2026-04-20 21:03:39</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -17173,10 +17173,10 @@
         </is>
       </c>
       <c r="K238" t="n">
-        <v>216554</v>
+        <v>216967</v>
       </c>
       <c r="L238" t="n">
-        <v>147.12</v>
+        <v>147.53</v>
       </c>
       <c r="M238" t="b">
         <v>0</v>
@@ -17197,7 +17197,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>2026-04-20 08:42:34</t>
+          <t>2026-04-20 21:03:40</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -17244,10 +17244,10 @@
         </is>
       </c>
       <c r="K239" t="n">
-        <v>216554</v>
+        <v>216967</v>
       </c>
       <c r="L239" t="n">
-        <v>147.12</v>
+        <v>147.53</v>
       </c>
       <c r="M239" t="b">
         <v>0</v>
@@ -17268,7 +17268,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>2026-04-20 08:42:36</t>
+          <t>2026-04-20 21:03:43</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -17315,10 +17315,10 @@
         </is>
       </c>
       <c r="K240" t="n">
-        <v>216554</v>
+        <v>216967</v>
       </c>
       <c r="L240" t="n">
-        <v>147.12</v>
+        <v>147.53</v>
       </c>
       <c r="M240" t="b">
         <v>0</v>
@@ -17339,7 +17339,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>2026-04-20 08:42:36</t>
+          <t>2026-04-20 21:03:43</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -17386,10 +17386,10 @@
         </is>
       </c>
       <c r="K241" t="n">
-        <v>216554</v>
+        <v>216967</v>
       </c>
       <c r="L241" t="n">
-        <v>147.12</v>
+        <v>147.53</v>
       </c>
       <c r="M241" t="b">
         <v>0</v>
@@ -17410,7 +17410,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>2026-04-20 08:42:37</t>
+          <t>2026-04-20 21:03:44</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -17457,10 +17457,10 @@
         </is>
       </c>
       <c r="K242" t="n">
-        <v>220900</v>
+        <v>222000</v>
       </c>
       <c r="L242" t="n">
-        <v>150.07</v>
+        <v>150.95</v>
       </c>
       <c r="M242" t="b">
         <v>0</v>
@@ -17481,7 +17481,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>2026-04-20 08:42:41</t>
+          <t>2026-04-20 21:03:47</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -17528,7 +17528,7 @@
         </is>
       </c>
       <c r="K243" t="n">
-        <v>230658</v>
+        <v>230456</v>
       </c>
       <c r="L243" t="n">
         <v>156.7</v>
@@ -17552,7 +17552,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>2026-04-20 08:42:41</t>
+          <t>2026-04-20 21:03:48</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -17599,10 +17599,10 @@
         </is>
       </c>
       <c r="K244" t="n">
-        <v>171750</v>
+        <v>172077</v>
       </c>
       <c r="L244" t="n">
-        <v>116.68</v>
+        <v>117</v>
       </c>
       <c r="M244" t="b">
         <v>1</v>
@@ -17623,7 +17623,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>2026-04-20 08:42:41</t>
+          <t>2026-04-20 21:03:48</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -17670,10 +17670,10 @@
         </is>
       </c>
       <c r="K245" t="n">
-        <v>171750</v>
+        <v>172077</v>
       </c>
       <c r="L245" t="n">
-        <v>116.68</v>
+        <v>117</v>
       </c>
       <c r="M245" t="b">
         <v>1</v>
@@ -17694,7 +17694,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>2026-04-20 08:42:43</t>
+          <t>2026-04-20 21:03:49</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -17741,10 +17741,10 @@
         </is>
       </c>
       <c r="K246" t="n">
-        <v>171750</v>
+        <v>172077</v>
       </c>
       <c r="L246" t="n">
-        <v>116.68</v>
+        <v>117</v>
       </c>
       <c r="M246" t="b">
         <v>1</v>
@@ -17765,7 +17765,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>2026-04-20 08:42:43</t>
+          <t>2026-04-20 21:03:49</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -17812,10 +17812,10 @@
         </is>
       </c>
       <c r="K247" t="n">
-        <v>171750</v>
+        <v>172077</v>
       </c>
       <c r="L247" t="n">
-        <v>116.68</v>
+        <v>117</v>
       </c>
       <c r="M247" t="b">
         <v>1</v>
@@ -17836,7 +17836,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>2026-04-20 08:42:45</t>
+          <t>2026-04-20 21:03:51</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -17883,10 +17883,10 @@
         </is>
       </c>
       <c r="K248" t="n">
-        <v>171750</v>
+        <v>172077</v>
       </c>
       <c r="L248" t="n">
-        <v>116.68</v>
+        <v>117</v>
       </c>
       <c r="M248" t="b">
         <v>1</v>
@@ -17907,7 +17907,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>2026-04-20 08:42:45</t>
+          <t>2026-04-20 21:03:51</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -17954,10 +17954,10 @@
         </is>
       </c>
       <c r="K249" t="n">
-        <v>171750</v>
+        <v>172077</v>
       </c>
       <c r="L249" t="n">
-        <v>116.68</v>
+        <v>117</v>
       </c>
       <c r="M249" t="b">
         <v>1</v>
@@ -17978,7 +17978,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>2026-04-20 08:42:47</t>
+          <t>2026-04-20 21:03:53</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -18025,10 +18025,10 @@
         </is>
       </c>
       <c r="K250" t="n">
-        <v>171750</v>
+        <v>172077</v>
       </c>
       <c r="L250" t="n">
-        <v>116.68</v>
+        <v>117</v>
       </c>
       <c r="M250" t="b">
         <v>1</v>
@@ -18049,7 +18049,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>2026-04-20 08:42:47</t>
+          <t>2026-04-20 21:03:53</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -18096,10 +18096,10 @@
         </is>
       </c>
       <c r="K251" t="n">
-        <v>171750</v>
+        <v>172077</v>
       </c>
       <c r="L251" t="n">
-        <v>116.68</v>
+        <v>117</v>
       </c>
       <c r="M251" t="b">
         <v>1</v>
@@ -18120,7 +18120,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>2026-04-20 08:42:49</t>
+          <t>2026-04-20 21:03:55</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -18167,10 +18167,10 @@
         </is>
       </c>
       <c r="K252" t="n">
-        <v>171750</v>
+        <v>172077</v>
       </c>
       <c r="L252" t="n">
-        <v>116.68</v>
+        <v>117</v>
       </c>
       <c r="M252" t="b">
         <v>1</v>
@@ -18191,7 +18191,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>2026-04-20 08:42:49</t>
+          <t>2026-04-20 21:03:55</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -18238,10 +18238,10 @@
         </is>
       </c>
       <c r="K253" t="n">
-        <v>171750</v>
+        <v>172077</v>
       </c>
       <c r="L253" t="n">
-        <v>116.68</v>
+        <v>117</v>
       </c>
       <c r="M253" t="b">
         <v>1</v>
@@ -18262,7 +18262,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>2026-04-20 08:42:50</t>
+          <t>2026-04-20 21:03:57</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="K254" t="n">
-        <v>171750</v>
+        <v>172077</v>
       </c>
       <c r="L254" t="n">
-        <v>116.68</v>
+        <v>117</v>
       </c>
       <c r="M254" t="b">
         <v>1</v>
@@ -18333,7 +18333,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>2026-04-20 08:42:50</t>
+          <t>2026-04-20 21:03:57</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -18380,10 +18380,10 @@
         </is>
       </c>
       <c r="K255" t="n">
-        <v>171750</v>
+        <v>172077</v>
       </c>
       <c r="L255" t="n">
-        <v>116.68</v>
+        <v>117</v>
       </c>
       <c r="M255" t="b">
         <v>1</v>
@@ -18404,7 +18404,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>2026-04-20 08:42:53</t>
+          <t>2026-04-20 21:03:59</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -18451,10 +18451,10 @@
         </is>
       </c>
       <c r="K256" t="n">
-        <v>171750</v>
+        <v>172077</v>
       </c>
       <c r="L256" t="n">
-        <v>116.68</v>
+        <v>117</v>
       </c>
       <c r="M256" t="b">
         <v>1</v>
@@ -18475,7 +18475,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>2026-04-20 08:42:53</t>
+          <t>2026-04-20 21:03:59</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -18522,10 +18522,10 @@
         </is>
       </c>
       <c r="K257" t="n">
-        <v>171750</v>
+        <v>172077</v>
       </c>
       <c r="L257" t="n">
-        <v>116.68</v>
+        <v>117</v>
       </c>
       <c r="M257" t="b">
         <v>1</v>
@@ -18546,7 +18546,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>2026-04-20 08:42:55</t>
+          <t>2026-04-20 21:04:01</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -18593,10 +18593,10 @@
         </is>
       </c>
       <c r="K258" t="n">
-        <v>171750</v>
+        <v>172077</v>
       </c>
       <c r="L258" t="n">
-        <v>116.68</v>
+        <v>117</v>
       </c>
       <c r="M258" t="b">
         <v>1</v>
@@ -18617,7 +18617,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>2026-04-20 08:42:55</t>
+          <t>2026-04-20 21:04:01</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -18664,10 +18664,10 @@
         </is>
       </c>
       <c r="K259" t="n">
-        <v>171750</v>
+        <v>172077</v>
       </c>
       <c r="L259" t="n">
-        <v>116.68</v>
+        <v>117</v>
       </c>
       <c r="M259" t="b">
         <v>1</v>
@@ -18688,7 +18688,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>2026-04-20 08:42:57</t>
+          <t>2026-04-20 21:04:03</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -18735,10 +18735,10 @@
         </is>
       </c>
       <c r="K260" t="n">
-        <v>171750</v>
+        <v>172077</v>
       </c>
       <c r="L260" t="n">
-        <v>116.68</v>
+        <v>117</v>
       </c>
       <c r="M260" t="b">
         <v>1</v>
@@ -18759,7 +18759,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>2026-04-20 08:42:57</t>
+          <t>2026-04-20 21:04:03</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -18806,10 +18806,10 @@
         </is>
       </c>
       <c r="K261" t="n">
-        <v>171750</v>
+        <v>172077</v>
       </c>
       <c r="L261" t="n">
-        <v>116.68</v>
+        <v>117</v>
       </c>
       <c r="M261" t="b">
         <v>1</v>
@@ -18830,7 +18830,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>2026-04-20 08:42:58</t>
+          <t>2026-04-20 21:04:05</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -18877,10 +18877,10 @@
         </is>
       </c>
       <c r="K262" t="n">
-        <v>171750</v>
+        <v>172077</v>
       </c>
       <c r="L262" t="n">
-        <v>116.68</v>
+        <v>117</v>
       </c>
       <c r="M262" t="b">
         <v>1</v>
@@ -18901,7 +18901,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>2026-04-20 08:42:58</t>
+          <t>2026-04-20 21:04:05</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -18948,10 +18948,10 @@
         </is>
       </c>
       <c r="K263" t="n">
-        <v>171750</v>
+        <v>172077</v>
       </c>
       <c r="L263" t="n">
-        <v>116.68</v>
+        <v>117</v>
       </c>
       <c r="M263" t="b">
         <v>1</v>
@@ -18972,7 +18972,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>2026-04-20 08:43:00</t>
+          <t>2026-04-20 21:04:07</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -19019,10 +19019,10 @@
         </is>
       </c>
       <c r="K264" t="n">
-        <v>171750</v>
+        <v>172077</v>
       </c>
       <c r="L264" t="n">
-        <v>116.68</v>
+        <v>117</v>
       </c>
       <c r="M264" t="b">
         <v>1</v>
@@ -19043,7 +19043,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>2026-04-20 08:43:00</t>
+          <t>2026-04-20 21:04:07</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -19090,10 +19090,10 @@
         </is>
       </c>
       <c r="K265" t="n">
-        <v>171750</v>
+        <v>172077</v>
       </c>
       <c r="L265" t="n">
-        <v>116.68</v>
+        <v>117</v>
       </c>
       <c r="M265" t="b">
         <v>1</v>
@@ -19114,7 +19114,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>2026-04-20 08:43:02</t>
+          <t>2026-04-20 21:04:09</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -19161,10 +19161,10 @@
         </is>
       </c>
       <c r="K266" t="n">
-        <v>171750</v>
+        <v>172077</v>
       </c>
       <c r="L266" t="n">
-        <v>116.68</v>
+        <v>117</v>
       </c>
       <c r="M266" t="b">
         <v>1</v>
@@ -19185,7 +19185,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>2026-04-20 08:43:02</t>
+          <t>2026-04-20 21:04:09</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -19232,10 +19232,10 @@
         </is>
       </c>
       <c r="K267" t="n">
-        <v>171750</v>
+        <v>172077</v>
       </c>
       <c r="L267" t="n">
-        <v>116.68</v>
+        <v>117</v>
       </c>
       <c r="M267" t="b">
         <v>1</v>
@@ -19256,7 +19256,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>2026-04-20 08:43:04</t>
+          <t>2026-04-20 21:04:10</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -19303,10 +19303,10 @@
         </is>
       </c>
       <c r="K268" t="n">
-        <v>171750</v>
+        <v>172077</v>
       </c>
       <c r="L268" t="n">
-        <v>116.68</v>
+        <v>117</v>
       </c>
       <c r="M268" t="b">
         <v>1</v>
@@ -19327,7 +19327,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>2026-04-20 08:43:04</t>
+          <t>2026-04-20 21:04:10</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -19374,10 +19374,10 @@
         </is>
       </c>
       <c r="K269" t="n">
-        <v>171750</v>
+        <v>172077</v>
       </c>
       <c r="L269" t="n">
-        <v>116.68</v>
+        <v>117</v>
       </c>
       <c r="M269" t="b">
         <v>1</v>
@@ -19398,7 +19398,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>2026-04-20 08:43:06</t>
+          <t>2026-04-20 21:04:13</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -19445,10 +19445,10 @@
         </is>
       </c>
       <c r="K270" t="n">
-        <v>171750</v>
+        <v>172077</v>
       </c>
       <c r="L270" t="n">
-        <v>116.68</v>
+        <v>117</v>
       </c>
       <c r="M270" t="b">
         <v>1</v>
@@ -19469,7 +19469,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>2026-04-20 08:43:06</t>
+          <t>2026-04-20 21:04:13</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -19516,10 +19516,10 @@
         </is>
       </c>
       <c r="K271" t="n">
-        <v>171750</v>
+        <v>172077</v>
       </c>
       <c r="L271" t="n">
-        <v>116.68</v>
+        <v>117</v>
       </c>
       <c r="M271" t="b">
         <v>1</v>
@@ -19540,7 +19540,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>2026-04-20 08:43:07</t>
+          <t>2026-04-20 21:04:14</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -19587,10 +19587,10 @@
         </is>
       </c>
       <c r="K272" t="n">
-        <v>203300</v>
+        <v>204300</v>
       </c>
       <c r="L272" t="n">
-        <v>138.11</v>
+        <v>138.91</v>
       </c>
       <c r="M272" t="b">
         <v>0</v>
@@ -19611,7 +19611,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>2026-04-20 08:43:08</t>
+          <t>2026-04-20 21:04:14</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -19658,10 +19658,10 @@
         </is>
       </c>
       <c r="K273" t="n">
-        <v>167269</v>
+        <v>167588</v>
       </c>
       <c r="L273" t="n">
-        <v>113.64</v>
+        <v>113.95</v>
       </c>
       <c r="M273" t="b">
         <v>1</v>
@@ -19682,7 +19682,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>2026-04-20 08:43:08</t>
+          <t>2026-04-20 21:04:14</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -19729,10 +19729,10 @@
         </is>
       </c>
       <c r="K274" t="n">
-        <v>167269</v>
+        <v>167588</v>
       </c>
       <c r="L274" t="n">
-        <v>113.64</v>
+        <v>113.95</v>
       </c>
       <c r="M274" t="b">
         <v>1</v>
@@ -19753,7 +19753,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>2026-04-20 08:43:10</t>
+          <t>2026-04-20 21:04:16</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -19800,10 +19800,10 @@
         </is>
       </c>
       <c r="K275" t="n">
-        <v>167269</v>
+        <v>167588</v>
       </c>
       <c r="L275" t="n">
-        <v>113.64</v>
+        <v>113.95</v>
       </c>
       <c r="M275" t="b">
         <v>1</v>
@@ -19824,7 +19824,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>2026-04-20 08:43:10</t>
+          <t>2026-04-20 21:04:16</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -19871,10 +19871,10 @@
         </is>
       </c>
       <c r="K276" t="n">
-        <v>167269</v>
+        <v>167588</v>
       </c>
       <c r="L276" t="n">
-        <v>113.64</v>
+        <v>113.95</v>
       </c>
       <c r="M276" t="b">
         <v>1</v>
@@ -19895,7 +19895,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>2026-04-20 08:43:11</t>
+          <t>2026-04-20 21:04:18</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -19942,10 +19942,10 @@
         </is>
       </c>
       <c r="K277" t="n">
-        <v>167269</v>
+        <v>167588</v>
       </c>
       <c r="L277" t="n">
-        <v>113.64</v>
+        <v>113.95</v>
       </c>
       <c r="M277" t="b">
         <v>1</v>
@@ -19966,7 +19966,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>2026-04-20 08:43:11</t>
+          <t>2026-04-20 21:04:18</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -20013,10 +20013,10 @@
         </is>
       </c>
       <c r="K278" t="n">
-        <v>167269</v>
+        <v>167588</v>
       </c>
       <c r="L278" t="n">
-        <v>113.64</v>
+        <v>113.95</v>
       </c>
       <c r="M278" t="b">
         <v>1</v>
@@ -20037,7 +20037,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>2026-04-20 08:43:13</t>
+          <t>2026-04-20 21:04:20</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -20084,10 +20084,10 @@
         </is>
       </c>
       <c r="K279" t="n">
-        <v>167269</v>
+        <v>167588</v>
       </c>
       <c r="L279" t="n">
-        <v>113.64</v>
+        <v>113.95</v>
       </c>
       <c r="M279" t="b">
         <v>1</v>
@@ -20108,7 +20108,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>2026-04-20 08:43:13</t>
+          <t>2026-04-20 21:04:20</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -20155,10 +20155,10 @@
         </is>
       </c>
       <c r="K280" t="n">
-        <v>167269</v>
+        <v>167588</v>
       </c>
       <c r="L280" t="n">
-        <v>113.64</v>
+        <v>113.95</v>
       </c>
       <c r="M280" t="b">
         <v>1</v>
@@ -20179,7 +20179,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>2026-04-20 08:43:15</t>
+          <t>2026-04-20 21:04:22</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -20226,10 +20226,10 @@
         </is>
       </c>
       <c r="K281" t="n">
-        <v>167269</v>
+        <v>167588</v>
       </c>
       <c r="L281" t="n">
-        <v>113.64</v>
+        <v>113.95</v>
       </c>
       <c r="M281" t="b">
         <v>1</v>
@@ -20250,7 +20250,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>2026-04-20 08:43:15</t>
+          <t>2026-04-20 21:04:22</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -20297,10 +20297,10 @@
         </is>
       </c>
       <c r="K282" t="n">
-        <v>167269</v>
+        <v>167588</v>
       </c>
       <c r="L282" t="n">
-        <v>113.64</v>
+        <v>113.95</v>
       </c>
       <c r="M282" t="b">
         <v>1</v>
@@ -20321,7 +20321,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>2026-04-20 08:43:17</t>
+          <t>2026-04-20 21:04:24</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -20368,10 +20368,10 @@
         </is>
       </c>
       <c r="K283" t="n">
-        <v>167269</v>
+        <v>167588</v>
       </c>
       <c r="L283" t="n">
-        <v>113.64</v>
+        <v>113.95</v>
       </c>
       <c r="M283" t="b">
         <v>1</v>
@@ -20392,7 +20392,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>2026-04-20 08:43:17</t>
+          <t>2026-04-20 21:04:24</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -20439,10 +20439,10 @@
         </is>
       </c>
       <c r="K284" t="n">
-        <v>167269</v>
+        <v>167588</v>
       </c>
       <c r="L284" t="n">
-        <v>113.64</v>
+        <v>113.95</v>
       </c>
       <c r="M284" t="b">
         <v>1</v>
@@ -20463,7 +20463,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>2026-04-20 08:43:19</t>
+          <t>2026-04-20 21:04:26</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -20510,10 +20510,10 @@
         </is>
       </c>
       <c r="K285" t="n">
-        <v>167269</v>
+        <v>167588</v>
       </c>
       <c r="L285" t="n">
-        <v>113.64</v>
+        <v>113.95</v>
       </c>
       <c r="M285" t="b">
         <v>1</v>
@@ -20534,7 +20534,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>2026-04-20 08:43:19</t>
+          <t>2026-04-20 21:04:26</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -20581,10 +20581,10 @@
         </is>
       </c>
       <c r="K286" t="n">
-        <v>167269</v>
+        <v>167588</v>
       </c>
       <c r="L286" t="n">
-        <v>113.64</v>
+        <v>113.95</v>
       </c>
       <c r="M286" t="b">
         <v>1</v>
@@ -20605,7 +20605,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>2026-04-20 08:43:21</t>
+          <t>2026-04-20 21:04:28</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -20652,10 +20652,10 @@
         </is>
       </c>
       <c r="K287" t="n">
-        <v>167269</v>
+        <v>167588</v>
       </c>
       <c r="L287" t="n">
-        <v>113.64</v>
+        <v>113.95</v>
       </c>
       <c r="M287" t="b">
         <v>1</v>
@@ -20676,7 +20676,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>2026-04-20 08:43:21</t>
+          <t>2026-04-20 21:04:28</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -20723,10 +20723,10 @@
         </is>
       </c>
       <c r="K288" t="n">
-        <v>167269</v>
+        <v>167588</v>
       </c>
       <c r="L288" t="n">
-        <v>113.64</v>
+        <v>113.95</v>
       </c>
       <c r="M288" t="b">
         <v>1</v>
@@ -20747,7 +20747,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>2026-04-20 08:43:22</t>
+          <t>2026-04-20 21:04:30</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -20794,10 +20794,10 @@
         </is>
       </c>
       <c r="K289" t="n">
-        <v>167269</v>
+        <v>167588</v>
       </c>
       <c r="L289" t="n">
-        <v>113.64</v>
+        <v>113.95</v>
       </c>
       <c r="M289" t="b">
         <v>1</v>
@@ -20818,7 +20818,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>2026-04-20 08:43:22</t>
+          <t>2026-04-20 21:04:30</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -20865,10 +20865,10 @@
         </is>
       </c>
       <c r="K290" t="n">
-        <v>167269</v>
+        <v>167588</v>
       </c>
       <c r="L290" t="n">
-        <v>113.64</v>
+        <v>113.95</v>
       </c>
       <c r="M290" t="b">
         <v>1</v>
@@ -20889,7 +20889,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>2026-04-20 08:43:24</t>
+          <t>2026-04-20 21:04:32</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -20936,10 +20936,10 @@
         </is>
       </c>
       <c r="K291" t="n">
-        <v>167269</v>
+        <v>167588</v>
       </c>
       <c r="L291" t="n">
-        <v>113.64</v>
+        <v>113.95</v>
       </c>
       <c r="M291" t="b">
         <v>1</v>
@@ -20960,7 +20960,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>2026-04-20 08:43:24</t>
+          <t>2026-04-20 21:04:32</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -21007,10 +21007,10 @@
         </is>
       </c>
       <c r="K292" t="n">
-        <v>167269</v>
+        <v>167588</v>
       </c>
       <c r="L292" t="n">
-        <v>113.64</v>
+        <v>113.95</v>
       </c>
       <c r="M292" t="b">
         <v>1</v>
@@ -21031,7 +21031,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>2026-04-20 08:43:26</t>
+          <t>2026-04-20 21:04:33</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -21078,10 +21078,10 @@
         </is>
       </c>
       <c r="K293" t="n">
-        <v>167269</v>
+        <v>167588</v>
       </c>
       <c r="L293" t="n">
-        <v>113.64</v>
+        <v>113.95</v>
       </c>
       <c r="M293" t="b">
         <v>1</v>
@@ -21102,7 +21102,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>2026-04-20 08:43:26</t>
+          <t>2026-04-20 21:04:33</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -21149,10 +21149,10 @@
         </is>
       </c>
       <c r="K294" t="n">
-        <v>167269</v>
+        <v>167588</v>
       </c>
       <c r="L294" t="n">
-        <v>113.64</v>
+        <v>113.95</v>
       </c>
       <c r="M294" t="b">
         <v>1</v>
@@ -21173,7 +21173,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>2026-04-20 08:43:28</t>
+          <t>2026-04-20 21:04:35</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -21220,10 +21220,10 @@
         </is>
       </c>
       <c r="K295" t="n">
-        <v>167269</v>
+        <v>167588</v>
       </c>
       <c r="L295" t="n">
-        <v>113.64</v>
+        <v>113.95</v>
       </c>
       <c r="M295" t="b">
         <v>1</v>
@@ -21244,7 +21244,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>2026-04-20 08:43:28</t>
+          <t>2026-04-20 21:04:35</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -21291,10 +21291,10 @@
         </is>
       </c>
       <c r="K296" t="n">
-        <v>167269</v>
+        <v>167588</v>
       </c>
       <c r="L296" t="n">
-        <v>113.64</v>
+        <v>113.95</v>
       </c>
       <c r="M296" t="b">
         <v>1</v>
@@ -21315,7 +21315,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>2026-04-20 08:43:30</t>
+          <t>2026-04-20 21:04:37</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -21362,10 +21362,10 @@
         </is>
       </c>
       <c r="K297" t="n">
-        <v>167269</v>
+        <v>167588</v>
       </c>
       <c r="L297" t="n">
-        <v>113.64</v>
+        <v>113.95</v>
       </c>
       <c r="M297" t="b">
         <v>1</v>
@@ -21386,7 +21386,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>2026-04-20 08:43:30</t>
+          <t>2026-04-20 21:04:37</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -21433,10 +21433,10 @@
         </is>
       </c>
       <c r="K298" t="n">
-        <v>167269</v>
+        <v>167588</v>
       </c>
       <c r="L298" t="n">
-        <v>113.64</v>
+        <v>113.95</v>
       </c>
       <c r="M298" t="b">
         <v>1</v>
@@ -21457,7 +21457,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>2026-04-20 08:43:32</t>
+          <t>2026-04-20 21:04:39</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -21504,10 +21504,10 @@
         </is>
       </c>
       <c r="K299" t="n">
-        <v>167269</v>
+        <v>167588</v>
       </c>
       <c r="L299" t="n">
-        <v>113.64</v>
+        <v>113.95</v>
       </c>
       <c r="M299" t="b">
         <v>1</v>
@@ -21528,7 +21528,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>2026-04-20 08:43:32</t>
+          <t>2026-04-20 21:04:39</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -21575,10 +21575,10 @@
         </is>
       </c>
       <c r="K300" t="n">
-        <v>167269</v>
+        <v>167588</v>
       </c>
       <c r="L300" t="n">
-        <v>113.64</v>
+        <v>113.95</v>
       </c>
       <c r="M300" t="b">
         <v>1</v>
@@ -21599,7 +21599,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>2026-04-20 08:43:33</t>
+          <t>2026-04-20 21:04:41</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -21662,7 +21662,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>2026-04-20 08:43:34</t>
+          <t>2026-04-20 21:04:41</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -21725,7 +21725,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>2026-04-20 08:43:34</t>
+          <t>2026-04-20 21:04:41</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -21788,7 +21788,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>2026-04-20 08:43:36</t>
+          <t>2026-04-20 21:04:43</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -21851,7 +21851,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>2026-04-20 08:43:38</t>
+          <t>2026-04-20 21:04:45</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -21914,7 +21914,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>2026-04-20 08:43:39</t>
+          <t>2026-04-20 21:04:47</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -21977,7 +21977,7 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>2026-04-20 08:43:41</t>
+          <t>2026-04-20 21:04:49</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -22040,7 +22040,7 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>2026-04-20 08:43:43</t>
+          <t>2026-04-20 21:04:50</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -22103,7 +22103,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>2026-04-20 08:43:45</t>
+          <t>2026-04-20 21:04:52</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -22166,7 +22166,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>2026-04-20 08:43:47</t>
+          <t>2026-04-20 21:04:54</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -22229,7 +22229,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>2026-04-20 08:43:49</t>
+          <t>2026-04-20 21:04:56</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -22292,7 +22292,7 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>2026-04-20 08:43:50</t>
+          <t>2026-04-20 21:04:58</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -22355,7 +22355,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>2026-04-20 08:43:52</t>
+          <t>2026-04-20 21:05:00</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -22418,7 +22418,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>2026-04-20 08:43:54</t>
+          <t>2026-04-20 21:05:02</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -22481,7 +22481,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>2026-04-20 08:43:56</t>
+          <t>2026-04-20 21:05:04</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -22544,7 +22544,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>2026-04-20 08:43:58</t>
+          <t>2026-04-20 21:05:06</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -22607,7 +22607,7 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>2026-04-20 08:43:59</t>
+          <t>2026-04-20 21:05:07</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
